--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 55825-2023</t>
+          <t>A 42922-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45239</v>
+        <v>45182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,169 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Talltita
+Tjockfotad fingersvamp
+Björksplintborre
+Granbarkgnagare
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 55825-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>46</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1124,164 +1248,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 42922-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45182</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>47</v>
-      </c>
-      <c r="U6" t="n">
-        <v>47</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Talltita
-Tjockfotad fingersvamp
-Björksplintborre
-Granbarkgnagare
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 61763-2025</t>
+          <t>A 50435-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46002</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,11 +1564,16 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1577,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1589,21 +1594,138 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Talltita
+Aprikosfingersvamp
+Mindre märgborre
+Mönjevaxing
+Nästrot
+Tibast
+Blåsippa
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 61763-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Dunmossa
@@ -1616,158 +1738,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 50435-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45601</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Talltita
-Aprikosfingersvamp
-Mindre märgborre
-Mönjevaxing
-Nästrot
-Tibast
-Blåsippa
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 63543-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2409,597 +2409,597 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>46191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>45139</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45756</v>
+        <v>46090</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,19 +3676,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3722,42 +3717,46 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3771,10 +3770,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45448</v>
+        <v>46090</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3787,16 +3786,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3811,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3823,46 +3822,50 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3876,10 +3879,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45456</v>
+        <v>45965</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3892,7 +3895,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>22.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3928,46 +3931,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3981,10 +3984,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>45965</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3997,17 +4000,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -4021,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4033,50 +4036,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4090,10 +4089,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46090</v>
+        <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4106,17 +4105,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -4130,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4142,50 +4141,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4199,10 +4194,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4215,7 +4210,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4251,46 +4246,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4304,10 +4299,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45965</v>
+        <v>46142</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4320,16 +4315,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4344,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4360,42 +4355,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4405,14 +4400,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45965</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4420,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>22.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4458,49 +4453,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46142</v>
+        <v>45756</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,14 +4524,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4570,42 +4570,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4619,10 +4619,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44560</v>
+        <v>45139</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4634,23 +4634,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4664,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4680,42 +4675,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4729,10 +4724,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45756</v>
+        <v>45456</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4744,23 +4739,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4774,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4783,49 +4773,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4835,14 +4825,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46142</v>
+        <v>44560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4854,17 +4844,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4879,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4888,49 +4883,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4944,10 +4939,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45139</v>
+        <v>45756</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4959,17 +4954,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4993,42 +4993,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45205</v>
+        <v>45226</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44946</v>
+        <v>46028</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5963,14 +5963,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45260</v>
+        <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6026,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45394</v>
+        <v>46055</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44587</v>
+        <v>44917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45259</v>
+        <v>45819</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44606</v>
+        <v>45932</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45832</v>
+        <v>45932</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6391,7 +6391,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45769</v>
+        <v>45000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6420,13 +6420,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6469,7 +6464,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6483,10 +6478,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45000</v>
+        <v>45394</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6499,7 +6494,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6542,7 +6537,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6556,10 +6551,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45819</v>
+        <v>45756</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6571,8 +6566,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45932</v>
+        <v>45194</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6702,10 +6702,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45932</v>
+        <v>45107</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6844,14 +6844,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46102</v>
+        <v>45382</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45050</v>
+        <v>46102</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6980,7 +6980,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45063</v>
+        <v>44649</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7063,14 +7063,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45071</v>
+        <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45461</v>
+        <v>45084</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44597</v>
+        <v>46002</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7282,14 +7282,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45328</v>
+        <v>44597</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45260</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45086</v>
+        <v>45397</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46028</v>
+        <v>45356</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46055</v>
+        <v>46171</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7593,8 +7593,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7637,7 +7642,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7651,10 +7656,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45084</v>
+        <v>46178</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7667,7 +7672,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7710,7 +7715,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7720,14 +7725,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45382</v>
+        <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7740,7 +7745,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7783,7 +7788,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7797,10 +7802,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45586</v>
+        <v>46092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7813,7 +7818,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7856,7 +7861,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7866,14 +7871,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45328</v>
+        <v>45397</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7886,7 +7891,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7929,7 +7934,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7946,7 +7951,7 @@
         <v>45225</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7959,7 +7964,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8002,7 +8007,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8016,10 +8021,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45728</v>
+        <v>45205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8032,7 +8037,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8075,7 +8080,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8089,10 +8094,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45394</v>
+        <v>45225</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8105,7 +8110,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8148,7 +8153,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8162,10 +8167,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46171</v>
+        <v>45310</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8177,13 +8182,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45225</v>
+        <v>45063</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46178</v>
+        <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46178</v>
+        <v>46258</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45450</v>
+        <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45310</v>
+        <v>45139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46092</v>
+        <v>45139</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8674,14 +8674,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44917</v>
+        <v>45000</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8737,7 +8737,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44586</v>
+        <v>44609</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8810,7 +8810,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44637</v>
+        <v>45586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44706</v>
+        <v>45064</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45000</v>
+        <v>44706</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9039,14 +9039,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45356</v>
+        <v>45078</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9058,8 +9058,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46258</v>
+        <v>44587</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9132,7 +9137,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9175,7 +9180,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9189,10 +9194,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46258</v>
+        <v>45450</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9205,7 +9210,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9248,7 +9253,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9262,10 +9267,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46258</v>
+        <v>44946</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9278,7 +9283,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9321,7 +9326,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9335,10 +9340,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45139</v>
+        <v>45050</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9351,7 +9356,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9394,7 +9399,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9404,14 +9409,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45139</v>
+        <v>45328</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9467,7 +9472,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9481,10 +9486,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45078</v>
+        <v>44586</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9496,13 +9501,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44609</v>
+        <v>45545</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44649</v>
+        <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45107</v>
+        <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45064</v>
+        <v>45071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45194</v>
+        <v>45035</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45194</v>
+        <v>45303</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45397</v>
+        <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45303</v>
+        <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10143,10 +10143,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45397</v>
+        <v>45769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10158,8 +10158,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10202,7 +10207,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10216,10 +10221,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45035</v>
+        <v>45728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10232,7 +10237,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10275,7 +10280,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10289,10 +10294,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45545</v>
+        <v>45394</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10305,7 +10310,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10348,7 +10353,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10362,10 +10367,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45756</v>
+        <v>45194</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10377,13 +10382,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45383</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45193</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45261</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 55825-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45182</v>
+        <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,297 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blodticka
+Flagellkvastmossa
+Jättesvampmal
+Mindre märgborre
+Vedticka
+Mattlummer
+Spillkråka
+Tjäder
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 50718-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45217</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>43</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenticka
+Tallticka
+Ullticka
+Vedtrappmossa
+Brandticka
+Bronshjon
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Gulnål
+Rödgul trumpetsvamp
+Trådticka
+Vedticka
+Blåsippa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1124,288 +1376,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 55825-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blodticka
-Flagellkvastmossa
-Jättesvampmal
-Mindre märgborre
-Vedticka
-Mattlummer
-Spillkråka
-Tjäder
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50718-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45217</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>43</v>
-      </c>
-      <c r="U7" t="n">
-        <v>43</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenticka
-Tallticka
-Ullticka
-Vedtrappmossa
-Brandticka
-Bronshjon
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Gulnål
-Rödgul trumpetsvamp
-Trådticka
-Vedticka
-Blåsippa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50435-2024</t>
+          <t>A 61763-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>46002</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,16 +1564,11 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1582,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1594,21 +1589,143 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Dunmossa
+Talltita
+Björksplintborre
+Blomkålssvamp
+Mörk husmossa
+Stubbspretmossa
+Vågbandad barkbock
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 50435-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
         <v>16</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>15</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Talltita
@@ -1621,153 +1738,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 61763-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Dunmossa
-Talltita
-Björksplintborre
-Blomkålssvamp
-Mörk husmossa
-Stubbspretmossa
-Vågbandad barkbock
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63543-2025</t>
+          <t>A 14508-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46013</v>
+        <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2409,597 +2409,597 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hussvala
+Berggräsfjäril
+Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
 Björksplintborre</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 48717-2024</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45593</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>6.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Tjäder
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 9807-2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>8</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 9745-2022</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>44618</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>5.9</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>4</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Vedticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14508-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45394</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hussvala
-Berggräsfjäril
-Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41021-2023</t>
+          <t>A 27935-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45173</v>
+        <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,16 +3359,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3392,262 +3392,262 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 41021-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Fjällig taggsvamp s.str.
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>9</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46090</v>
+        <v>45756</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,14 +3676,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3710,53 +3715,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3770,10 +3771,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46090</v>
+        <v>45756</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3785,14 +3786,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3822,50 +3828,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3879,10 +3881,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3895,7 +3897,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>22.9</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3935,42 +3937,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3984,10 +3986,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4000,16 +4002,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4024,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4036,46 +4038,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4089,10 +4095,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44973</v>
+        <v>46090</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4105,16 +4111,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4129,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4141,46 +4147,50 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4194,10 +4204,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4210,7 +4220,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4250,42 +4260,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4299,10 +4309,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46142</v>
+        <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,17 +4325,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>22.9</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4339,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4355,42 +4365,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4400,14 +4410,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>45456</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4420,7 +4430,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4453,49 +4463,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4509,10 +4519,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45756</v>
+        <v>45139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,23 +4534,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4554,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4566,46 +4571,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4619,10 +4624,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45139</v>
+        <v>46142</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4635,16 +4640,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4659,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4671,46 +4676,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4724,10 +4729,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45456</v>
+        <v>44973</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4740,7 +4745,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.4</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4780,42 +4785,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4825,14 +4830,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44560</v>
+        <v>46142</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4844,23 +4849,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4883,49 +4883,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45756</v>
+        <v>44560</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4993,42 +4993,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44603</v>
+        <v>45205</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45226</v>
+        <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45086</v>
+        <v>45225</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46028</v>
+        <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45832</v>
+        <v>44946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6026,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6036,14 +6036,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46055</v>
+        <v>45260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6109,14 +6109,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44917</v>
+        <v>45450</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45819</v>
+        <v>45310</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45932</v>
+        <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45932</v>
+        <v>46090</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6391,7 +6391,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6405,10 +6405,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45000</v>
+        <v>46102</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45394</v>
+        <v>44587</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45756</v>
+        <v>45259</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6566,13 +6566,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>9.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6615,7 +6610,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6629,10 +6624,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45194</v>
+        <v>44606</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6645,7 +6640,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6688,7 +6683,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6702,10 +6697,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45107</v>
+        <v>45932</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6718,7 +6713,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6761,7 +6756,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6775,10 +6770,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46090</v>
+        <v>45932</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6791,7 +6786,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6834,7 +6829,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6848,10 +6843,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45382</v>
+        <v>44917</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6864,7 +6859,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6907,7 +6902,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6917,14 +6912,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46102</v>
+        <v>45328</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6937,7 +6932,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6980,7 +6975,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6994,10 +6989,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44649</v>
+        <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7009,8 +7004,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7063,14 +7063,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45328</v>
+        <v>45000</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45084</v>
+        <v>44586</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46002</v>
+        <v>44637</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44597</v>
+        <v>44706</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45260</v>
+        <v>46002</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45397</v>
+        <v>45000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45356</v>
+        <v>45050</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7574,14 +7574,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46171</v>
+        <v>45356</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7593,13 +7593,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7642,7 +7637,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7656,10 +7651,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46178</v>
+        <v>46028</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7672,7 +7667,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7715,7 +7710,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7729,10 +7724,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46178</v>
+        <v>45063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7745,7 +7740,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7788,7 +7783,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7802,10 +7797,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46092</v>
+        <v>45071</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7818,7 +7813,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7861,7 +7856,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7871,14 +7866,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45397</v>
+        <v>45461</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7891,7 +7886,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7934,7 +7929,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7948,10 +7943,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45225</v>
+        <v>44597</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7964,7 +7959,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8007,7 +8002,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8021,10 +8016,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45205</v>
+        <v>46171</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8036,8 +8031,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45225</v>
+        <v>46055</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45310</v>
+        <v>46178</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45063</v>
+        <v>46178</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46258</v>
+        <v>45086</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46258</v>
+        <v>46092</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46258</v>
+        <v>45139</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8535,7 +8535,7 @@
         <v>45139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8620,8 +8620,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8664,7 +8669,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8678,10 +8683,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45000</v>
+        <v>45084</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8694,7 +8699,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8737,7 +8742,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8747,14 +8752,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44609</v>
+        <v>45382</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8767,7 +8772,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8827,7 +8832,7 @@
         <v>45586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8883,7 +8888,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8897,10 +8902,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45064</v>
+        <v>44609</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8913,7 +8918,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8956,7 +8961,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8970,10 +8975,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44706</v>
+        <v>44649</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8986,7 +8991,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9029,7 +9034,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9039,14 +9044,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45078</v>
+        <v>45328</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9058,13 +9063,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44587</v>
+        <v>45225</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45450</v>
+        <v>45107</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44946</v>
+        <v>45064</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45050</v>
+        <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9409,14 +9409,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45328</v>
+        <v>46258</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44586</v>
+        <v>45194</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45545</v>
+        <v>45194</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44637</v>
+        <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45461</v>
+        <v>45728</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9774,14 +9774,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45071</v>
+        <v>45397</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45035</v>
+        <v>45303</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45303</v>
+        <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45259</v>
+        <v>45397</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44606</v>
+        <v>45035</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10143,10 +10143,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45769</v>
+        <v>45545</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10158,13 +10158,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10207,7 +10202,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10221,10 +10216,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45728</v>
+        <v>45756</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10236,8 +10231,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10280,7 +10280,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45394</v>
+        <v>45364</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10353,7 +10353,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10367,10 +10367,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45194</v>
+        <v>45383</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45364</v>
+        <v>45193</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45383</v>
+        <v>45261</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10572,7 +10572,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45193</v>
+        <v>45832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45261</v>
+        <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 55825-2023</t>
+          <t>A 42922-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45239</v>
+        <v>45182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,169 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Talltita
+Tjockfotad fingersvamp
+Björksplintborre
+Granbarkgnagare
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 55825-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>46</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1124,115 +1248,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 50718-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45217</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>3.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>9</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>16</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>43</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>43</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenticka
 Tallticka
@@ -1252,160 +1376,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 42922-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45182</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>47</v>
-      </c>
-      <c r="U7" t="n">
-        <v>47</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Talltita
-Tjockfotad fingersvamp
-Björksplintborre
-Granbarkgnagare
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 61763-2025</t>
+          <t>A 50435-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46002</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,11 +1564,16 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1577,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1589,21 +1594,138 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Talltita
+Aprikosfingersvamp
+Mindre märgborre
+Mönjevaxing
+Nästrot
+Tibast
+Blåsippa
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 61763-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Dunmossa
@@ -1616,158 +1738,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 50435-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45601</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Talltita
-Aprikosfingersvamp
-Mindre märgborre
-Mönjevaxing
-Nästrot
-Tibast
-Blåsippa
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 48717-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>45593</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -2382,624 +2382,624 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27935-2026</t>
+          <t>A 41021-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46191</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,17 +3359,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3392,262 +3392,262 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 41021-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,23 +3676,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>5.2</v>
+        <v>22.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3706,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3715,49 +3710,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3771,10 +3766,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3786,23 +3781,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3816,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3832,42 +3822,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3881,10 +3871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45448</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3897,7 +3887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3933,46 +3923,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3986,10 +3976,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4002,17 +3992,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -4026,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4038,43 +4028,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
@@ -4098,7 +4084,7 @@
         <v>46090</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4190,7 +4176,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4204,10 +4190,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4220,16 +4206,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4244,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4256,46 +4242,50 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4309,10 +4299,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45965</v>
+        <v>45756</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4324,17 +4314,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4349,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4365,42 +4360,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4414,10 +4409,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45456</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4430,16 +4425,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4454,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4466,39 +4461,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
@@ -4522,7 +4517,7 @@
         <v>45139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4610,7 +4605,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4624,10 +4619,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46142</v>
+        <v>45456</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4640,17 +4635,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4664,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4676,46 +4671,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4725,14 +4720,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44973</v>
+        <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4745,7 +4740,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4778,49 +4773,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4830,14 +4825,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46142</v>
+        <v>44560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4849,17 +4844,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4883,49 +4883,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4939,10 +4939,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44560</v>
+        <v>45756</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4960,13 +4960,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4993,42 +4993,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45205</v>
+        <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44603</v>
+        <v>45086</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45225</v>
+        <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45226</v>
+        <v>46028</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5963,14 +5963,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44946</v>
+        <v>44917</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6026,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6036,14 +6036,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45260</v>
+        <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45450</v>
+        <v>45000</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45310</v>
+        <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45394</v>
+        <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6274,8 +6274,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6318,7 +6323,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6332,10 +6337,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46090</v>
+        <v>45819</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6348,7 +6353,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6391,7 +6396,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6405,10 +6410,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46102</v>
+        <v>45194</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6464,7 +6469,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6478,10 +6483,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44587</v>
+        <v>45107</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6494,7 +6499,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6537,7 +6542,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6551,10 +6556,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45259</v>
+        <v>45932</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6567,7 +6572,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6610,7 +6615,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6624,10 +6629,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44606</v>
+        <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6640,7 +6645,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6683,7 +6688,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6693,14 +6698,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45932</v>
+        <v>45382</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6713,7 +6718,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6756,7 +6761,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6770,10 +6775,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45932</v>
+        <v>46055</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6786,7 +6791,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6829,7 +6834,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6839,14 +6844,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44917</v>
+        <v>44649</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6859,7 +6864,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6902,7 +6907,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6912,14 +6917,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45328</v>
+        <v>45084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6932,7 +6937,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6975,7 +6980,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6989,10 +6994,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45769</v>
+        <v>46090</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7004,13 +7009,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45000</v>
+        <v>46002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44586</v>
+        <v>44597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44637</v>
+        <v>45260</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44706</v>
+        <v>46102</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46002</v>
+        <v>45397</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45000</v>
+        <v>45356</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45050</v>
+        <v>45397</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7564,7 +7564,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7574,14 +7574,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45356</v>
+        <v>45225</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7651,10 +7651,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46028</v>
+        <v>45205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7724,10 +7724,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45063</v>
+        <v>45225</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7783,7 +7783,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45071</v>
+        <v>45310</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7856,7 +7856,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7870,10 +7870,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45461</v>
+        <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7929,7 +7929,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7939,14 +7939,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44597</v>
+        <v>45328</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8002,7 +8002,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8016,10 +8016,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46171</v>
+        <v>45139</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8031,13 +8031,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8080,7 +8075,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8094,10 +8089,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46055</v>
+        <v>45139</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8110,7 +8105,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8153,7 +8148,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8167,10 +8162,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46178</v>
+        <v>45000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8183,7 +8178,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8226,7 +8221,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8240,10 +8235,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46178</v>
+        <v>44609</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8256,7 +8251,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8299,7 +8294,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8313,10 +8308,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45086</v>
+        <v>45586</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8329,7 +8324,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8372,7 +8367,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8386,10 +8381,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46092</v>
+        <v>45064</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8402,7 +8397,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8445,7 +8440,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8459,10 +8454,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45139</v>
+        <v>44706</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8475,7 +8470,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8518,7 +8513,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8532,10 +8527,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45139</v>
+        <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8547,8 +8542,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45078</v>
+        <v>46171</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -8669,7 +8669,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45084</v>
+        <v>44587</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8752,14 +8752,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45382</v>
+        <v>45450</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8815,7 +8815,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8829,10 +8829,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45586</v>
+        <v>44946</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8888,7 +8888,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44609</v>
+        <v>46178</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8975,10 +8975,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44649</v>
+        <v>46178</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9034,7 +9034,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9044,14 +9044,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45328</v>
+        <v>45050</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9107,7 +9107,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9117,14 +9117,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45225</v>
+        <v>45328</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9180,7 +9180,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9194,10 +9194,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45107</v>
+        <v>46092</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45064</v>
+        <v>44586</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9326,7 +9326,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9340,10 +9340,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46258</v>
+        <v>45545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9399,7 +9399,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46258</v>
+        <v>44637</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9472,7 +9472,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45194</v>
+        <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45194</v>
+        <v>46258</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9635,7 +9635,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45728</v>
+        <v>46258</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9774,14 +9774,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45397</v>
+        <v>45071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45303</v>
+        <v>45035</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45394</v>
+        <v>45303</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9997,10 +9997,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45397</v>
+        <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45035</v>
+        <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10143,10 +10143,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45545</v>
+        <v>45769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10158,8 +10158,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10202,7 +10207,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10216,10 +10221,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45756</v>
+        <v>45728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10231,13 +10236,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10280,7 +10280,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45364</v>
+        <v>45394</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10353,7 +10353,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10367,10 +10367,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45383</v>
+        <v>45194</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45193</v>
+        <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45261</v>
+        <v>45383</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10572,7 +10572,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45832</v>
+        <v>45193</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45819</v>
+        <v>45261</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 55825-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45182</v>
+        <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,173 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blodticka
+Flagellkvastmossa
+Jättesvampmal
+Mindre märgborre
+Vedticka
+Mattlummer
+Spillkråka
+Tjäder
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1124,164 +1252,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 55825-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blodticka
-Flagellkvastmossa
-Jättesvampmal
-Mindre märgborre
-Vedticka
-Mattlummer
-Spillkråka
-Tjäder
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 48717-2024</t>
+          <t>A 14508-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45593</v>
+        <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -2382,11 +2382,11 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
         <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hussvala
+Berggräsfjäril
+Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Tjäder
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14508-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45394</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hussvala
-Berggräsfjäril
-Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63539-2025</t>
+          <t>A 27935-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3233,14 +3233,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46013</v>
+        <v>46191</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,16 +3253,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3286,368 +3286,368 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 41021-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 63539-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vårärt</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 41021-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="D27" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45965</v>
+        <v>45756</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,17 +3676,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>22.9</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3701,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3717,42 +3722,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3766,10 +3771,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3782,7 +3787,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3822,42 +3827,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>46090</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3887,16 +3892,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3911,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3927,42 +3932,46 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3976,10 +3985,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>46090</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3992,16 +4001,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4016,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4032,42 +4041,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4081,10 +4094,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46090</v>
+        <v>45456</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,17 +4110,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -4121,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4133,50 +4146,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4190,10 +4199,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46090</v>
+        <v>44973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4206,17 +4215,17 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4230,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4246,46 +4255,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45756</v>
+        <v>46142</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4314,19 +4319,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4360,42 +4360,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4405,14 +4405,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,17 +4425,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4458,49 +4458,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45139</v>
+        <v>44560</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,17 +4529,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4554,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4570,42 +4575,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4619,10 +4624,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45456</v>
+        <v>45965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4635,7 +4640,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4671,46 +4676,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4720,14 +4725,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46142</v>
+        <v>45965</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4740,7 +4745,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>22.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4773,49 +4778,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4829,10 +4834,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44560</v>
+        <v>45756</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4850,13 +4855,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4883,49 +4888,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4939,10 +4944,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45756</v>
+        <v>45139</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4954,23 +4959,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4993,42 +4993,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45086</v>
+        <v>45205</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5824,7 +5824,7 @@
         <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,10 +5894,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46028</v>
+        <v>44946</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44917</v>
+        <v>45260</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6026,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45832</v>
+        <v>45394</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6099,7 +6099,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45000</v>
+        <v>44587</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45394</v>
+        <v>45259</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>9.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45756</v>
+        <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6274,13 +6274,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6323,7 +6318,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6337,10 +6332,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45819</v>
+        <v>45832</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6353,7 +6348,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6396,7 +6391,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6410,10 +6405,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45194</v>
+        <v>45769</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6425,8 +6420,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6483,10 +6483,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45107</v>
+        <v>45000</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45932</v>
+        <v>46090</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45932</v>
+        <v>45819</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6698,14 +6698,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45382</v>
+        <v>46102</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46055</v>
+        <v>45328</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44649</v>
+        <v>45050</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45084</v>
+        <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6980,7 +6980,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6994,10 +6994,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46090</v>
+        <v>45071</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46002</v>
+        <v>45461</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7143,7 +7143,7 @@
         <v>44597</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7209,14 +7209,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45260</v>
+        <v>45932</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46102</v>
+        <v>45932</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45397</v>
+        <v>45086</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45356</v>
+        <v>46171</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7447,8 +7447,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7491,7 +7496,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7501,14 +7506,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45397</v>
+        <v>45084</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7521,7 +7526,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7564,7 +7569,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7574,14 +7579,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45225</v>
+        <v>45382</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7594,7 +7599,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7637,7 +7642,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7651,10 +7656,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45205</v>
+        <v>45586</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7667,7 +7672,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7710,7 +7715,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7724,10 +7729,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45225</v>
+        <v>46178</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7740,7 +7745,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7783,7 +7788,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7797,10 +7802,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45310</v>
+        <v>46178</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7813,7 +7818,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7856,7 +7861,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7870,10 +7875,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45063</v>
+        <v>46092</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7886,7 +7891,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7929,7 +7934,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7946,7 +7951,7 @@
         <v>45328</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7959,7 +7964,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8002,7 +8007,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8016,10 +8021,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45139</v>
+        <v>45225</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8032,7 +8037,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8075,7 +8080,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8089,10 +8094,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45139</v>
+        <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8105,7 +8110,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8148,7 +8153,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8162,10 +8167,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45000</v>
+        <v>45394</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8178,7 +8183,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8221,7 +8226,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8235,10 +8240,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44609</v>
+        <v>45225</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8251,7 +8256,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8294,7 +8299,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8308,10 +8313,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45586</v>
+        <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8324,7 +8329,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8367,7 +8372,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45064</v>
+        <v>46258</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8397,7 +8402,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8440,7 +8445,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8454,10 +8459,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44706</v>
+        <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8470,7 +8475,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8513,7 +8518,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8527,10 +8532,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45078</v>
+        <v>45450</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8542,13 +8547,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46171</v>
+        <v>45310</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8620,13 +8620,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>5.7</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8669,7 +8664,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8683,10 +8678,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44587</v>
+        <v>46002</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8699,7 +8694,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8742,7 +8737,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8752,14 +8747,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45450</v>
+        <v>44917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8772,7 +8767,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8815,7 +8810,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8829,10 +8824,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44946</v>
+        <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8845,7 +8840,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8888,7 +8883,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8902,10 +8897,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46178</v>
+        <v>46028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8918,7 +8913,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8961,7 +8956,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8975,10 +8970,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46178</v>
+        <v>44637</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8991,7 +8986,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9034,7 +9029,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9048,10 +9043,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45050</v>
+        <v>44706</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9064,7 +9059,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9107,7 +9102,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9117,14 +9112,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45328</v>
+        <v>45000</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9137,7 +9132,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9180,7 +9175,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9190,14 +9185,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46092</v>
+        <v>45356</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9210,7 +9205,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9253,7 +9248,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9267,10 +9262,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44586</v>
+        <v>46055</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9283,7 +9278,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9326,7 +9321,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9340,10 +9335,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45545</v>
+        <v>45139</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9356,7 +9351,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9399,7 +9394,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9413,10 +9408,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44637</v>
+        <v>45139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9429,7 +9424,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9472,7 +9467,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9486,10 +9481,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45461</v>
+        <v>45078</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9501,8 +9496,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46258</v>
+        <v>44609</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46258</v>
+        <v>44649</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46258</v>
+        <v>45107</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45071</v>
+        <v>45064</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45035</v>
+        <v>45194</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45303</v>
+        <v>45194</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45259</v>
+        <v>45397</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10056,7 +10056,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10070,10 +10070,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44606</v>
+        <v>45303</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10129,7 +10129,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10143,10 +10143,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45769</v>
+        <v>45397</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10158,13 +10158,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10207,7 +10202,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10221,10 +10216,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45728</v>
+        <v>45035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10237,7 +10232,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10280,7 +10275,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10294,10 +10289,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45394</v>
+        <v>45545</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10310,7 +10305,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10353,7 +10348,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10367,10 +10362,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45194</v>
+        <v>45756</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10382,8 +10377,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10443,7 +10443,7 @@
         <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45383</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45193</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45261</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 50718-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45182</v>
+        <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1218,21 +1218,145 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>16</v>
       </c>
       <c r="T6" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>43</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenticka
+Tallticka
+Ullticka
+Vedtrappmossa
+Brandticka
+Bronshjon
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Gulnål
+Rödgul trumpetsvamp
+Trådticka
+Vedticka
+Blåsippa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
         <v>47</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>47</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1252,160 +1376,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50718-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45217</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>43</v>
-      </c>
-      <c r="U7" t="n">
-        <v>43</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenticka
-Tallticka
-Ullticka
-Vedtrappmossa
-Brandticka
-Bronshjon
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Gulnål
-Rödgul trumpetsvamp
-Trådticka
-Vedticka
-Blåsippa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 9745-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>44618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 27935-2026</t>
+          <t>A 41021-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3233,14 +3233,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46191</v>
+        <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,17 +3253,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3286,368 +3286,368 @@
         <v>2</v>
       </c>
       <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 63539-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vårärt</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 41021-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 63539-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vårärt</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45756</v>
+        <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3676,23 +3676,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3706,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3718,39 +3713,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
@@ -3774,7 +3769,7 @@
         <v>45448</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3862,7 +3857,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46090</v>
+        <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3892,7 +3887,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3928,50 +3923,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3985,10 +3976,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46090</v>
+        <v>45965</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4001,17 +3992,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.9</v>
+        <v>22.9</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -4025,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4041,46 +4032,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4094,10 +4081,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45456</v>
+        <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4110,7 +4097,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4146,46 +4133,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4199,10 +4186,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>45756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4214,17 +4201,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4239,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4251,46 +4243,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4304,10 +4296,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46142</v>
+        <v>45139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4320,17 +4312,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4344,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4356,46 +4348,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4405,14 +4397,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>45456</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4425,7 +4417,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4458,49 +4450,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4510,14 +4502,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44560</v>
+        <v>46142</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,23 +4521,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4559,7 +4546,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4568,49 +4555,49 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4624,10 +4611,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45965</v>
+        <v>44560</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4639,17 +4626,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4664,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4676,46 +4668,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4729,10 +4721,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4745,16 +4737,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>22.9</v>
+        <v>5.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4769,7 +4761,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4785,42 +4777,46 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4834,10 +4830,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45756</v>
+        <v>46090</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4849,19 +4845,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4888,49 +4879,53 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4944,10 +4939,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45139</v>
+        <v>45756</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4959,17 +4954,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4993,42 +4993,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5748,10 +5748,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45205</v>
+        <v>45226</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5890,14 +5890,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44946</v>
+        <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5963,14 +5963,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45260</v>
+        <v>45000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6026,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45394</v>
+        <v>45756</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6055,8 +6055,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6099,7 +6104,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6113,10 +6118,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44587</v>
+        <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6129,7 +6134,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6172,7 +6177,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6186,10 +6191,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45259</v>
+        <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6202,7 +6207,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9.4</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6245,7 +6250,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6259,10 +6264,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44606</v>
+        <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6275,7 +6280,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6318,7 +6323,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6328,14 +6333,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45832</v>
+        <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6348,7 +6353,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6391,7 +6396,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6405,10 +6410,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45769</v>
+        <v>44649</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6420,13 +6425,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6469,7 +6469,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6479,14 +6479,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45000</v>
+        <v>45328</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6542,7 +6542,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6556,10 +6556,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46090</v>
+        <v>45084</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6615,7 +6615,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45819</v>
+        <v>44597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6698,14 +6698,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46102</v>
+        <v>45260</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6761,7 +6761,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6771,14 +6771,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45328</v>
+        <v>45932</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6834,7 +6834,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45050</v>
+        <v>45932</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45063</v>
+        <v>45397</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6980,7 +6980,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6990,14 +6990,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45071</v>
+        <v>45356</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7063,14 +7063,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45461</v>
+        <v>45397</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44597</v>
+        <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7199,7 +7199,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45932</v>
+        <v>45205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7272,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45932</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45086</v>
+        <v>45310</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46171</v>
+        <v>45063</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7447,13 +7447,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7496,7 +7491,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7510,10 +7505,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45084</v>
+        <v>45139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7526,7 +7521,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7569,7 +7564,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7579,14 +7574,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45382</v>
+        <v>45139</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7642,7 +7637,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7656,10 +7651,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45586</v>
+        <v>45000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7672,7 +7667,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7715,7 +7710,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7729,10 +7724,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46178</v>
+        <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7745,7 +7740,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7788,7 +7783,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7802,10 +7797,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46178</v>
+        <v>45586</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7818,7 +7813,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7861,7 +7856,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7875,10 +7870,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46092</v>
+        <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7891,7 +7886,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7934,7 +7929,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7944,14 +7939,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45328</v>
+        <v>46028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7964,7 +7959,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8007,7 +8002,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8021,10 +8016,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45225</v>
+        <v>46171</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8036,8 +8031,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45728</v>
+        <v>45064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45394</v>
+        <v>44706</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45225</v>
+        <v>45078</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8255,8 +8255,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8299,7 +8304,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8313,10 +8318,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46258</v>
+        <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8329,7 +8334,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8372,7 +8377,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8386,10 +8391,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46258</v>
+        <v>46178</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8402,7 +8407,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8445,7 +8450,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8459,10 +8464,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46258</v>
+        <v>46178</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8475,7 +8480,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8518,7 +8523,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8532,10 +8537,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45450</v>
+        <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8548,7 +8553,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8591,7 +8596,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8605,10 +8610,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45310</v>
+        <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8621,7 +8626,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8664,7 +8669,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8678,10 +8683,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46002</v>
+        <v>44946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8694,7 +8699,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8737,7 +8742,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8747,14 +8752,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44917</v>
+        <v>45050</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8767,7 +8772,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8810,7 +8815,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8824,10 +8829,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44586</v>
+        <v>46090</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8840,7 +8845,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8883,7 +8888,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8897,10 +8902,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46028</v>
+        <v>46092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8913,7 +8918,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8956,7 +8961,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8966,14 +8971,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44637</v>
+        <v>45328</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8986,7 +8991,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9029,7 +9034,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9043,10 +9048,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44706</v>
+        <v>46102</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9059,7 +9064,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9102,7 +9107,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9116,10 +9121,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45000</v>
+        <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9132,7 +9137,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9175,7 +9180,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9185,14 +9190,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45356</v>
+        <v>45545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9205,7 +9210,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9248,7 +9253,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9262,10 +9267,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46055</v>
+        <v>44637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9278,7 +9283,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9321,7 +9326,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9335,10 +9340,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45139</v>
+        <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9351,7 +9356,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9394,7 +9399,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9408,10 +9413,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45139</v>
+        <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9424,7 +9429,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9467,7 +9472,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9481,10 +9486,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45078</v>
+        <v>45035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9496,13 +9501,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>5.7</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9545,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44609</v>
+        <v>45303</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44649</v>
+        <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9691,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9705,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45107</v>
+        <v>45259</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>9.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9764,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45064</v>
+        <v>46258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9837,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9851,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45194</v>
+        <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9924,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45194</v>
+        <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +9983,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45397</v>
+        <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10012,8 +10012,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10056,7 +10061,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10070,10 +10075,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45303</v>
+        <v>45728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10086,7 +10091,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10129,7 +10134,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10143,10 +10148,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45397</v>
+        <v>45394</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10159,7 +10164,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10202,7 +10207,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10216,10 +10221,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45035</v>
+        <v>45194</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10232,7 +10237,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10275,7 +10280,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10289,10 +10294,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45545</v>
+        <v>45364</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10305,7 +10310,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10348,7 +10353,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10362,10 +10367,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45756</v>
+        <v>45383</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10377,13 +10382,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10440,10 +10440,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45364</v>
+        <v>45193</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45383</v>
+        <v>45261</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10572,7 +10572,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10586,10 +10586,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45193</v>
+        <v>45832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10645,7 +10645,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10659,10 +10659,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45261</v>
+        <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45182</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>44618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45593</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45394</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>46013</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44973</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45448</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>46142</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>45965</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>45139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>45456</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>46142</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>44560</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46090</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45756</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>45450</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44609</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44616</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
         <v>44560</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>44606</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>44465</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>44655</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45226</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         <v>45086</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44917</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>45000</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>45756</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45194</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45107</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>45382</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>44649</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45328</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>45084</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44597</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45260</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>45932</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45932</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45397</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45356</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45397</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45225</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45205</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45310</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45063</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45139</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>45139</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45000</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44609</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>45586</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>46002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>46028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>46171</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45064</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44706</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45078</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46178</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>46178</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44587</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45450</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44946</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45050</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>46090</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>46092</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45328</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>46102</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>45545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>44637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>45461</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>45071</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>45035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45303</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>45259</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>46258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44606</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45769</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45728</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45394</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45194</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45364</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45383</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45193</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45261</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45832</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44872</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE119"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 55825-2023</t>
+          <t>A 42922-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45239</v>
+        <v>45182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,169 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Talltita
+Tjockfotad fingersvamp
+Björksplintborre
+Granbarkgnagare
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 55825-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>46</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1124,115 +1248,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 50718-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45217</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>3.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>9</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>16</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>43</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>43</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenticka
 Tallticka
@@ -1252,160 +1376,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 42922-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45182</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>47</v>
-      </c>
-      <c r="U7" t="n">
-        <v>47</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Talltita
-Tjockfotad fingersvamp
-Björksplintborre
-Granbarkgnagare
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>44618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>46013</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45593</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>45394</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34460-2023</t>
+          <t>A 63539-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45139</v>
+        <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3395,146 +3395,146 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vårärt</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 63539-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vårärt</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
         <v>46191</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 39170-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44973</v>
+        <v>46287</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3701,58 +3701,59 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp
+Tallticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 39168-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3766,10 +3767,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45448</v>
+        <v>46287</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3782,13 +3783,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -3812,52 +3813,53 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka
+Bollvitmossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3871,10 +3873,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46142</v>
+        <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3887,17 +3889,17 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3911,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3923,46 +3925,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3976,10 +3978,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3992,7 +3994,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>22.9</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4032,42 +4034,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4081,10 +4083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45965</v>
+        <v>46142</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4097,16 +4099,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4121,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4137,42 +4139,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4186,10 +4188,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4201,23 +4203,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4231,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4247,42 +4244,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4296,10 +4293,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45139</v>
+        <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4312,7 +4309,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4348,46 +4345,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4397,14 +4394,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45456</v>
+        <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4417,7 +4414,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4450,49 +4447,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4502,14 +4499,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46142</v>
+        <v>45756</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4521,17 +4518,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4546,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4555,49 +4557,49 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4611,10 +4613,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44560</v>
+        <v>46090</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4626,13 +4628,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4668,46 +4665,50 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4724,7 +4725,7 @@
         <v>46090</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,7 +4738,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4773,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
@@ -4781,42 +4782,42 @@
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4830,10 +4831,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46090</v>
+        <v>45139</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4846,17 +4847,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4886,46 +4887,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4939,10 +4936,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45756</v>
+        <v>45456</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4954,23 +4951,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -4984,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4993,49 +4985,49 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5049,10 +5041,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45450</v>
+        <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5064,14 +5056,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5101,46 +5098,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8089-2022</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5154,10 +5151,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44609</v>
+        <v>45756</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5169,14 +5166,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5200,20 +5202,52 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="X42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="Y42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <v/>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9442-2022</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5227,10 +5261,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44616</v>
+        <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5243,13 +5277,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5273,20 +5307,52 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="W43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="X43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="Y43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <v/>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 178-2022</t>
+          <t>A 8089-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5300,10 +5366,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44560</v>
+        <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5315,13 +5381,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5364,7 +5425,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 242-2022</t>
+          <t>A 9442-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5378,10 +5439,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44560</v>
+        <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5393,13 +5454,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5442,7 +5498,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7276-2022</t>
+          <t>A 178-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5456,10 +5512,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44606</v>
+        <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5471,8 +5527,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5515,7 +5576,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 52377-2021</t>
+          <t>A 242-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5529,10 +5590,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44465</v>
+        <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5544,8 +5605,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5588,7 +5654,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 14725-2022</t>
+          <t>A 7276-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5598,14 +5664,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44655</v>
+        <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5618,7 +5684,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5661,7 +5727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 52377-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5675,10 +5741,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44603</v>
+        <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5691,7 +5757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5734,7 +5800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 14725-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5744,14 +5810,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45226</v>
+        <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5764,7 +5830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5807,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5821,10 +5887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45086</v>
+        <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5880,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5890,14 +5956,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44917</v>
+        <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5910,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5953,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5967,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45000</v>
+        <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5983,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6026,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6036,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45756</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6055,13 +6121,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6104,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6118,10 +6179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45394</v>
+        <v>45000</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6134,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6177,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6191,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45194</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6206,8 +6267,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6250,7 +6316,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6264,10 +6330,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45107</v>
+        <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6280,7 +6346,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6323,7 +6389,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6333,14 +6399,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45382</v>
+        <v>45107</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6353,7 +6419,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6396,7 +6462,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6410,10 +6476,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44649</v>
+        <v>45194</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6426,7 +6492,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6469,7 +6535,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6483,10 +6549,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45328</v>
+        <v>45382</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6499,7 +6565,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6542,7 +6608,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6556,10 +6622,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45084</v>
+        <v>44649</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6572,7 +6638,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6615,7 +6681,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6625,14 +6691,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44597</v>
+        <v>45328</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6645,7 +6711,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6688,7 +6754,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6698,14 +6764,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45260</v>
+        <v>45084</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6718,7 +6784,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6778,7 +6844,7 @@
         <v>45932</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6851,7 +6917,7 @@
         <v>45932</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6907,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6921,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45397</v>
+        <v>44597</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6937,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6980,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6994,10 +7060,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45356</v>
+        <v>45260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7010,7 +7076,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7053,7 +7119,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7063,14 +7129,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
         <v>45397</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7083,7 +7149,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7126,7 +7192,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7136,14 +7202,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45225</v>
+        <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7156,7 +7222,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7199,7 +7265,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7209,14 +7275,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45205</v>
+        <v>45397</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7229,7 +7295,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7272,7 +7338,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7286,10 +7352,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>46171</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7301,8 +7367,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7345,7 +7416,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7359,10 +7430,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45310</v>
+        <v>45225</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7375,7 +7446,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7418,7 +7489,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7432,10 +7503,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45063</v>
+        <v>45205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7448,7 +7519,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7491,7 +7562,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7505,10 +7576,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45139</v>
+        <v>45225</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7521,7 +7592,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7564,7 +7635,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7578,10 +7649,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45139</v>
+        <v>45310</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7594,7 +7665,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7637,7 +7708,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7651,10 +7722,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45000</v>
+        <v>45063</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7667,7 +7738,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7710,7 +7781,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7724,10 +7795,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44609</v>
+        <v>46002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7740,7 +7811,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7783,7 +7854,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7797,10 +7868,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45586</v>
+        <v>46178</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7813,7 +7884,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7856,7 +7927,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7870,10 +7941,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46002</v>
+        <v>45139</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7886,7 +7957,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7929,7 +8000,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7943,10 +8014,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46028</v>
+        <v>45139</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7959,7 +8030,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8002,7 +8073,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8016,10 +8087,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8031,13 +8102,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5.7</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8080,7 +8146,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8094,10 +8160,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45064</v>
+        <v>45000</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8110,7 +8176,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8153,7 +8219,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8167,10 +8233,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44706</v>
+        <v>46028</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8183,7 +8249,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8226,7 +8292,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8240,10 +8306,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45078</v>
+        <v>44609</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8255,13 +8321,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8321,7 +8382,7 @@
         <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8377,7 +8438,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8391,10 +8452,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46178</v>
+        <v>45586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8407,7 +8468,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8450,7 +8511,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8464,10 +8525,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46178</v>
+        <v>46092</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8480,7 +8541,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8523,7 +8584,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8537,10 +8598,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44587</v>
+        <v>46090</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8553,7 +8614,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8596,7 +8657,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8610,10 +8671,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45450</v>
+        <v>45064</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8626,7 +8687,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8669,7 +8730,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8683,10 +8744,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44946</v>
+        <v>44706</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8699,7 +8760,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8742,7 +8803,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8756,10 +8817,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45050</v>
+        <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8771,8 +8832,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8815,7 +8881,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8829,10 +8895,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46090</v>
+        <v>46102</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8845,7 +8911,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8888,7 +8954,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8902,10 +8968,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46092</v>
+        <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8918,7 +8984,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8961,7 +9027,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8971,14 +9037,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45328</v>
+        <v>45450</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8991,7 +9057,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9034,7 +9100,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9048,10 +9114,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46102</v>
+        <v>44946</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9064,7 +9130,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9107,7 +9173,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9121,10 +9187,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44586</v>
+        <v>45050</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9137,7 +9203,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9180,7 +9246,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9190,14 +9256,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45545</v>
+        <v>45328</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9210,7 +9276,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9253,7 +9319,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9267,10 +9333,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44637</v>
+        <v>46258</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9283,7 +9349,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9326,7 +9392,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9340,10 +9406,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45461</v>
+        <v>44586</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9356,7 +9422,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9399,7 +9465,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9413,10 +9479,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45071</v>
+        <v>46258</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9429,7 +9495,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9472,7 +9538,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9486,10 +9552,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45035</v>
+        <v>46258</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9502,7 +9568,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9545,7 +9611,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9559,10 +9625,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45303</v>
+        <v>45545</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9575,7 +9641,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9618,7 +9684,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9632,10 +9698,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46258</v>
+        <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9648,7 +9714,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9691,7 +9757,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9705,10 +9771,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45259</v>
+        <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9721,7 +9787,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>9.4</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9764,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9778,10 +9844,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46258</v>
+        <v>45071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9794,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9837,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9851,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46258</v>
+        <v>45035</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9867,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9910,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9924,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44606</v>
+        <v>45303</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9940,7 +10006,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9983,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9997,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45769</v>
+        <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10012,13 +10078,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10061,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10075,10 +10136,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45728</v>
+        <v>46287</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10134,7 +10195,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10148,10 +10209,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45394</v>
+        <v>44606</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10164,7 +10225,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10207,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10221,10 +10282,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45194</v>
+        <v>45769</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10236,8 +10297,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10280,7 +10346,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10294,10 +10360,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45364</v>
+        <v>45728</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10310,7 +10376,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10353,7 +10419,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10367,10 +10433,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45383</v>
+        <v>45394</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10383,7 +10449,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10426,7 +10492,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10440,10 +10506,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45193</v>
+        <v>45194</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10456,7 +10522,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10499,7 +10565,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10513,10 +10579,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45261</v>
+        <v>45364</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10529,7 +10595,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10572,7 +10638,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10586,10 +10652,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45832</v>
+        <v>45383</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10602,7 +10668,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10645,7 +10711,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10659,10 +10725,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45819</v>
+        <v>45193</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10675,7 +10741,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10718,148 +10784,367 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
+          <t>A 61027-2023</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>A 30902-2025</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>45832</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>A 28431-2025</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>45819</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>S 6321-2022</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D118" s="1" t="n">
+      <c r="D121" s="1" t="n">
         <v>44872</v>
       </c>
-      <c r="E118" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I118" t="n">
+      <c r="E121" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
         <v>0.1</v>
       </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0</v>
-      </c>
-      <c r="N118" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="P118" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>S 2547-2025</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D119" s="1" t="n">
+      <c r="D122" s="1" t="n">
         <v>45911</v>
       </c>
-      <c r="E119" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I119" t="n">
+      <c r="E122" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
         <v>1.9</v>
       </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" t="n">
-        <v>0</v>
-      </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="2" t="inlineStr"/>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 55825-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45182</v>
+        <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,297 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blodticka
+Flagellkvastmossa
+Jättesvampmal
+Mindre märgborre
+Vedticka
+Mattlummer
+Spillkråka
+Tjäder
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 50718-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45217</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>43</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenticka
+Tallticka
+Ullticka
+Vedtrappmossa
+Brandticka
+Bronshjon
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Gulnål
+Rödgul trumpetsvamp
+Trådticka
+Vedticka
+Blåsippa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1124,288 +1376,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 55825-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blodticka
-Flagellkvastmossa
-Jättesvampmal
-Mindre märgborre
-Vedticka
-Mattlummer
-Spillkråka
-Tjäder
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50718-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45217</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>43</v>
-      </c>
-      <c r="U7" t="n">
-        <v>43</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenticka
-Tallticka
-Ullticka
-Vedtrappmossa
-Brandticka
-Bronshjon
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Gulnål
-Rödgul trumpetsvamp
-Trådticka
-Vedticka
-Blåsippa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9745-2022</t>
+          <t>A 14508-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44618</v>
+        <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,20 +2373,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hussvala
+Berggräsfjäril
+Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Vedticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 63543-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>46013</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>3.4</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
 Björksplintborre</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>8</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14508-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45394</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hussvala
-Berggräsfjäril
-Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>46013</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34460-2023</t>
+          <t>A 39168-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45139</v>
+        <v>46287</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3501,358 +3501,358 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 39170-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 27935-2026</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>46191</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>5</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T29" t="n">
         <v>9</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 39170-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 39168-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>45450</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3994,16 +3994,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4034,42 +4034,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46142</v>
+        <v>45756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,14 +4098,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4139,42 +4144,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>22.9</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4244,42 +4249,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4293,10 +4298,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45965</v>
+        <v>44560</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4308,17 +4313,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4333,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4345,46 +4355,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4394,14 +4404,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46142</v>
+        <v>45965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,7 +4424,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4447,49 +4457,49 @@
         <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4503,10 +4513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4518,23 +4528,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4548,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4564,42 +4569,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46090</v>
+        <v>45456</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4629,17 +4634,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4653,7 +4658,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4665,50 +4670,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4722,10 +4723,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46090</v>
+        <v>45756</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4737,14 +4738,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4771,53 +4777,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4831,10 +4833,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45139</v>
+        <v>46090</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4847,16 +4849,16 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4871,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4887,42 +4889,46 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4936,10 +4942,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45456</v>
+        <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4952,16 +4958,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4976,7 +4982,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4988,46 +4994,50 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5041,10 +5051,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44560</v>
+        <v>45139</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5056,23 +5066,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -5086,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5102,42 +5107,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5151,10 +5156,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45756</v>
+        <v>46142</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,19 +5171,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5205,49 +5205,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45450</v>
+        <v>46142</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5277,17 +5277,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5310,42 +5310,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14725-2022</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44655</v>
+        <v>45261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>7.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 14725-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5883,14 +5883,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44603</v>
+        <v>44655</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45226</v>
+        <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45086</v>
+        <v>45050</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44917</v>
+        <v>45205</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45000</v>
+        <v>45063</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>45071</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6267,13 +6267,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45394</v>
+        <v>45461</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45107</v>
+        <v>44597</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45194</v>
+        <v>45226</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6545,14 +6540,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45382</v>
+        <v>44946</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6618,14 +6613,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44649</v>
+        <v>45260</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6691,14 +6686,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45328</v>
+        <v>45086</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6711,7 +6706,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45084</v>
+        <v>45394</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6841,10 +6836,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45932</v>
+        <v>45084</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6910,14 +6905,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45932</v>
+        <v>45382</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6925,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6973,7 +6968,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6987,10 +6982,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44597</v>
+        <v>45586</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +6998,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7046,7 +7041,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7056,14 +7051,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45260</v>
+        <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7071,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7119,7 +7114,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7133,10 +7128,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45397</v>
+        <v>45932</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7144,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7192,7 +7187,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7202,14 +7197,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45356</v>
+        <v>45932</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7217,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7265,7 +7260,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7275,14 +7270,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45397</v>
+        <v>45259</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7290,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7338,7 +7333,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7352,10 +7347,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46171</v>
+        <v>44606</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7367,13 +7362,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7416,7 +7406,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7426,14 +7416,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45225</v>
+        <v>45328</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7446,7 +7436,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7489,7 +7479,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7503,10 +7493,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45205</v>
+        <v>45225</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7519,7 +7509,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7562,7 +7552,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7576,10 +7566,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45225</v>
+        <v>45769</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7591,8 +7581,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7635,7 +7630,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7649,10 +7644,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45310</v>
+        <v>45000</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7665,7 +7660,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7708,7 +7703,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7722,10 +7717,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45063</v>
+        <v>45728</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7738,7 +7733,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7781,7 +7776,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7795,10 +7790,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46002</v>
+        <v>45394</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7811,7 +7806,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7854,7 +7849,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46178</v>
+        <v>45225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7884,7 +7879,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7927,7 +7922,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45139</v>
+        <v>45832</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7957,7 +7952,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8000,7 +7995,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45139</v>
+        <v>46028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8073,7 +8068,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8087,10 +8082,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46178</v>
+        <v>46002</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45000</v>
+        <v>45450</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8176,7 +8171,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8219,7 +8214,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8233,10 +8228,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46028</v>
+        <v>45310</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8249,7 +8244,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8292,7 +8287,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8306,10 +8301,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44609</v>
+        <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8322,7 +8317,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8365,7 +8360,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8375,14 +8370,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46055</v>
+        <v>44917</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8390,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45586</v>
+        <v>44586</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8463,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8511,7 +8506,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8525,10 +8520,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46092</v>
+        <v>46287</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8536,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8601,7 +8596,7 @@
         <v>46090</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8657,7 +8652,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45064</v>
+        <v>45819</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8687,7 +8682,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8730,7 +8725,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44706</v>
+        <v>44637</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8760,7 +8755,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8803,7 +8798,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8817,10 +8812,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45078</v>
+        <v>44706</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8832,13 +8827,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8881,7 +8871,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8895,10 +8885,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46102</v>
+        <v>45000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8911,7 +8901,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8954,7 +8944,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8964,14 +8954,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44587</v>
+        <v>45356</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8984,7 +8974,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9027,7 +9017,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9041,10 +9031,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45450</v>
+        <v>46102</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9047,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9100,7 +9090,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9114,10 +9104,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44946</v>
+        <v>45139</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9120,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9173,7 +9163,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9187,10 +9177,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45050</v>
+        <v>45139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9193,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9246,7 +9236,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9256,14 +9246,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45328</v>
+        <v>45078</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9275,8 +9265,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9319,7 +9314,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9329,14 +9324,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46258</v>
+        <v>45328</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9344,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9392,7 +9387,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9406,10 +9401,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44586</v>
+        <v>44609</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9417,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9465,7 +9460,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9479,10 +9474,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46258</v>
+        <v>44649</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9490,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9538,7 +9533,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9552,10 +9547,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46258</v>
+        <v>45107</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9563,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9611,7 +9606,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9625,10 +9620,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45545</v>
+        <v>45064</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9641,7 +9636,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9684,7 +9679,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9698,10 +9693,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44637</v>
+        <v>45194</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9709,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9757,7 +9752,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9771,10 +9766,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45461</v>
+        <v>45194</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9787,7 +9782,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9830,7 +9825,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9840,14 +9835,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45071</v>
+        <v>45397</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9855,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9903,7 +9898,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9917,10 +9912,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45035</v>
+        <v>45303</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9928,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9976,7 +9971,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9990,10 +9985,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45303</v>
+        <v>45397</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10001,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10049,7 +10044,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10063,10 +10058,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45259</v>
+        <v>45035</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10074,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10122,7 +10117,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 39163-2026</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10136,10 +10131,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46287</v>
+        <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10147,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10195,7 +10190,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10209,10 +10204,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44606</v>
+        <v>45756</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10224,8 +10219,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45769</v>
+        <v>45364</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10297,13 +10297,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10346,7 +10341,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10360,10 +10355,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45728</v>
+        <v>45383</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10376,7 +10371,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10419,7 +10414,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10433,10 +10428,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45394</v>
+        <v>45193</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10449,7 +10444,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10492,7 +10487,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10506,10 +10501,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45194</v>
+        <v>46171</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10521,8 +10516,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45364</v>
+        <v>46178</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10638,7 +10638,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45383</v>
+        <v>46178</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10711,7 +10711,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45193</v>
+        <v>46092</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10784,7 +10784,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45261</v>
+        <v>46258</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45832</v>
+        <v>46258</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45819</v>
+        <v>46258</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11020,7 +11020,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 55825-2023</t>
+          <t>A 42922-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45239</v>
+        <v>45182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,169 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Talltita
+Tjockfotad fingersvamp
+Björksplintborre
+Granbarkgnagare
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 55825-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>46</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1124,115 +1248,115 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 50718-2023</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45217</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>3.6</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>9</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>4</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>16</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>43</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>43</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Rosenticka
 Tallticka
@@ -1252,160 +1376,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 42922-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45182</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>47</v>
-      </c>
-      <c r="U7" t="n">
-        <v>47</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Talltita
-Tjockfotad fingersvamp
-Björksplintborre
-Granbarkgnagare
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>46002</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 9745-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>44618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J18" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>8</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63539-2025</t>
+          <t>A 34460-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46013</v>
+        <v>45139</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3395,464 +3395,464 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 63539-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vårärt</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 39170-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 39168-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>46287</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>6.8</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 39170-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>44973</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45450</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3994,17 +3994,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4034,42 +4034,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4098,23 +4098,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4144,42 +4139,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4193,10 +4188,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45448</v>
+        <v>45965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4249,42 +4244,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4298,10 +4293,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44560</v>
+        <v>46142</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4313,13 +4308,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -4355,46 +4345,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4408,10 +4398,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45965</v>
+        <v>45756</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4423,17 +4413,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4448,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4464,42 +4459,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4529,16 +4524,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>22.9</v>
+        <v>5.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4553,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4569,42 +4564,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4618,10 +4617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45456</v>
+        <v>46090</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4634,16 +4633,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4658,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4674,42 +4673,46 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4723,10 +4726,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45756</v>
+        <v>45139</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4738,23 +4741,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4768,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4777,49 +4775,49 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4829,14 +4827,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46090</v>
+        <v>46142</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4849,17 +4847,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4873,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4882,53 +4880,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4942,10 +4936,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46090</v>
+        <v>45456</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4958,17 +4952,17 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -4982,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4994,50 +4988,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5051,10 +5041,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45139</v>
+        <v>44560</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5066,17 +5056,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5091,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5107,42 +5102,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5156,10 +5151,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46142</v>
+        <v>45756</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5171,14 +5166,19 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5205,49 +5205,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46142</v>
+        <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5277,16 +5277,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5310,42 +5310,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 14725-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45261</v>
+        <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 14725-2022</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5883,14 +5883,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44655</v>
+        <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44603</v>
+        <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45050</v>
+        <v>45086</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45205</v>
+        <v>44917</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45063</v>
+        <v>45000</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45071</v>
+        <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6267,8 +6267,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6311,7 +6316,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6325,10 +6330,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45461</v>
+        <v>45394</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6341,7 +6346,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6384,7 +6389,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6398,10 +6403,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44597</v>
+        <v>45194</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6414,7 +6419,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6457,7 +6462,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6471,10 +6476,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45226</v>
+        <v>45107</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6487,7 +6492,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6530,7 +6535,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6540,14 +6545,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44946</v>
+        <v>45382</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6560,7 +6565,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6603,7 +6608,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6613,14 +6618,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45260</v>
+        <v>44649</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6633,7 +6638,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6676,7 +6681,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6686,14 +6691,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45086</v>
+        <v>45328</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45394</v>
+        <v>45084</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45084</v>
+        <v>45932</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6852,7 +6857,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6905,14 +6910,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45382</v>
+        <v>45932</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6925,7 +6930,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6968,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6982,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45586</v>
+        <v>44597</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6998,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7041,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7051,14 +7056,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44587</v>
+        <v>45260</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7071,7 +7076,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7114,7 +7119,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7128,10 +7133,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45932</v>
+        <v>45397</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7144,7 +7149,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7187,7 +7192,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7197,14 +7202,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45932</v>
+        <v>45356</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7217,7 +7222,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7260,7 +7265,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7270,14 +7275,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45259</v>
+        <v>45397</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7290,7 +7295,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7333,7 +7338,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7347,10 +7352,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44606</v>
+        <v>45225</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7363,7 +7368,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7406,7 +7411,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7416,14 +7421,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45328</v>
+        <v>45205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7436,7 +7441,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7496,7 +7501,7 @@
         <v>45225</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7552,7 +7557,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7566,10 +7571,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45769</v>
+        <v>45310</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7581,13 +7586,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45000</v>
+        <v>45063</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45728</v>
+        <v>46002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45394</v>
+        <v>45139</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45225</v>
+        <v>45139</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45832</v>
+        <v>45000</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8012,7 +8012,7 @@
         <v>46028</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46002</v>
+        <v>44609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45450</v>
+        <v>45586</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8228,10 +8228,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45310</v>
+        <v>46055</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46055</v>
+        <v>46171</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8316,8 +8316,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8370,14 +8375,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44917</v>
+        <v>45064</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8390,7 +8395,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8433,7 +8438,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44586</v>
+        <v>44706</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8463,7 +8468,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8506,7 +8511,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39163-2026</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8520,10 +8525,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46287</v>
+        <v>46090</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8536,7 +8541,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8579,7 +8584,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8593,10 +8598,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46090</v>
+        <v>45078</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8608,8 +8613,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8652,7 +8662,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8666,10 +8676,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45819</v>
+        <v>46178</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8682,7 +8692,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8725,7 +8735,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8739,10 +8749,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44637</v>
+        <v>46178</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8755,7 +8765,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8798,7 +8808,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8812,10 +8822,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44706</v>
+        <v>46102</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8828,7 +8838,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8871,7 +8881,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8885,10 +8895,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45000</v>
+        <v>44587</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8901,7 +8911,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8944,7 +8954,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8954,14 +8964,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45356</v>
+        <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8974,7 +8984,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9017,7 +9027,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9031,10 +9041,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46102</v>
+        <v>44946</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9047,7 +9057,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9090,7 +9100,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9104,10 +9114,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45139</v>
+        <v>46092</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9120,7 +9130,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9163,7 +9173,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9177,10 +9187,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45139</v>
+        <v>45050</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9193,7 +9203,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9236,7 +9246,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9246,14 +9256,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45078</v>
+        <v>45328</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9265,13 +9275,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9314,7 +9319,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9324,14 +9329,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45328</v>
+        <v>44586</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9344,7 +9349,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9387,7 +9392,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9401,10 +9406,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44609</v>
+        <v>45545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9417,7 +9422,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9460,7 +9465,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9474,10 +9479,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44649</v>
+        <v>44637</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9490,7 +9495,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9533,7 +9538,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9547,10 +9552,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45107</v>
+        <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9563,7 +9568,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9606,7 +9611,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9620,10 +9625,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45064</v>
+        <v>46258</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9636,7 +9641,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9679,7 +9684,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9693,10 +9698,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45194</v>
+        <v>46258</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9709,7 +9714,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9752,7 +9757,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9766,10 +9771,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45194</v>
+        <v>46258</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9782,7 +9787,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9825,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9835,14 +9840,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45397</v>
+        <v>45071</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9855,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9898,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9912,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45303</v>
+        <v>45035</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9928,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9971,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9985,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45397</v>
+        <v>45303</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10001,7 +10006,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10044,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10058,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45035</v>
+        <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10074,7 +10079,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10117,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10131,10 +10136,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45545</v>
+        <v>44606</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10147,7 +10152,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10190,7 +10195,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10204,10 +10209,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45756</v>
+        <v>45769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10230,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10268,7 +10273,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10282,10 +10287,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45364</v>
+        <v>45728</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10303,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10341,7 +10346,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10355,10 +10360,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45383</v>
+        <v>45394</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10376,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10414,7 +10419,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10428,10 +10433,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45193</v>
+        <v>45194</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10449,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10487,7 +10492,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10501,10 +10506,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46171</v>
+        <v>45364</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10516,13 +10521,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46178</v>
+        <v>45383</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10638,7 +10638,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46178</v>
+        <v>46287</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10711,7 +10711,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46092</v>
+        <v>45193</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10784,7 +10784,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46258</v>
+        <v>45261</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46258</v>
+        <v>45832</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46258</v>
+        <v>45819</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11020,7 +11020,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 55825-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45182</v>
+        <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,173 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blodticka
+Flagellkvastmossa
+Jättesvampmal
+Mindre märgborre
+Vedticka
+Mattlummer
+Spillkråka
+Tjäder
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1124,164 +1252,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 55825-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blodticka
-Flagellkvastmossa
-Jättesvampmal
-Mindre märgborre
-Vedticka
-Mattlummer
-Spillkråka
-Tjäder
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50435-2024</t>
+          <t>A 61763-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>46002</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,16 +1564,11 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1582,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1594,21 +1589,143 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Dunmossa
+Talltita
+Björksplintborre
+Blomkålssvamp
+Mörk husmossa
+Stubbspretmossa
+Vågbandad barkbock
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 50435-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
         <v>16</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>15</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Talltita
@@ -1621,153 +1738,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 61763-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Dunmossa
-Talltita
-Björksplintborre
-Blomkålssvamp
-Mörk husmossa
-Stubbspretmossa
-Vågbandad barkbock
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 9745-2022</t>
+          <t>A 14508-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44618</v>
+        <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,20 +2373,20 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hussvala
+Berggräsfjäril
+Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Vedticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14508-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45394</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hussvala
-Berggräsfjäril
-Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 41021-2023</t>
+          <t>A 63539-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45173</v>
+        <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3293,573 +3293,573 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t>Tallticka
+Vårärt</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 41021-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>Fjällig taggsvamp s.str.
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 39168-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 39170-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 34460-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D29" s="1" t="n">
         <v>45139</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>1.7</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>2</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 63539-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vårärt</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 39170-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 39168-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44973</v>
+        <v>45756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3888,17 +3888,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3913,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3925,39 +3930,39 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
@@ -3981,7 +3986,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4069,7 +4074,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4083,10 +4088,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4099,16 +4104,16 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>22.9</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4123,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4135,46 +4140,50 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4188,10 +4197,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,16 +4213,16 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4228,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4244,42 +4253,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4293,10 +4306,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46142</v>
+        <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4309,17 +4322,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4333,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4349,42 +4362,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4398,10 +4411,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45756</v>
+        <v>45965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4413,23 +4426,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>22.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4443,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4459,42 +4467,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4508,10 +4516,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46090</v>
+        <v>45456</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4524,17 +4532,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4548,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4560,50 +4568,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4617,10 +4621,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46090</v>
+        <v>44973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4633,17 +4637,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4657,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4673,46 +4677,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45139</v>
+        <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4742,16 +4742,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4778,39 +4778,39 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>46142</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45456</v>
+        <v>44560</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,17 +4951,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4976,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4992,42 +4997,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5041,10 +5046,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44560</v>
+        <v>45756</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5062,13 +5067,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5095,49 +5100,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5151,10 +5156,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45756</v>
+        <v>45139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5166,23 +5171,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5205,42 +5205,42 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
         <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45226</v>
+        <v>45205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45086</v>
+        <v>45226</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44917</v>
+        <v>44946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45000</v>
+        <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45756</v>
+        <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6267,13 +6267,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6316,7 +6311,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6330,10 +6325,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45394</v>
+        <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6346,7 +6341,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6403,10 +6398,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45194</v>
+        <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6419,7 +6414,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6462,7 +6457,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6476,10 +6471,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45107</v>
+        <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6492,7 +6487,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6535,7 +6530,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6545,14 +6540,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45382</v>
+        <v>45259</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6565,7 +6560,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6608,7 +6603,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6622,10 +6617,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44649</v>
+        <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6638,7 +6633,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6681,7 +6676,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6691,14 +6686,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45328</v>
+        <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6711,7 +6706,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6754,7 +6749,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6768,10 +6763,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45084</v>
+        <v>45932</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6784,7 +6779,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6827,7 +6822,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6841,10 +6836,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45932</v>
+        <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6857,7 +6852,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6900,7 +6895,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45932</v>
+        <v>45769</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6929,8 +6924,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44597</v>
+        <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7056,14 +7056,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45260</v>
+        <v>46102</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45397</v>
+        <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7202,14 +7202,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45356</v>
+        <v>46002</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7275,14 +7275,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45397</v>
+        <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45225</v>
+        <v>45063</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45205</v>
+        <v>45071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45225</v>
+        <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45310</v>
+        <v>44597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45063</v>
+        <v>45832</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7717,10 +7717,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46002</v>
+        <v>45086</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7790,10 +7790,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45139</v>
+        <v>45819</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45139</v>
+        <v>46171</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7878,8 +7878,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7922,7 +7927,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45000</v>
+        <v>46178</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7952,7 +7957,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7995,7 +8000,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46028</v>
+        <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8025,7 +8030,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8068,7 +8073,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8082,10 +8087,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44609</v>
+        <v>46178</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8141,7 +8146,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8151,14 +8156,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45586</v>
+        <v>45382</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8171,7 +8176,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8214,7 +8219,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46055</v>
+        <v>45586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8244,7 +8249,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8287,7 +8292,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8301,10 +8306,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46171</v>
+        <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8316,13 +8321,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45064</v>
+        <v>45328</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44706</v>
+        <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46090</v>
+        <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8584,7 +8584,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45078</v>
+        <v>46258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8613,13 +8613,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8662,7 +8657,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8676,10 +8671,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46178</v>
+        <v>45728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8692,7 +8687,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8735,7 +8730,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8749,10 +8744,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46178</v>
+        <v>46258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8765,7 +8760,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8808,7 +8803,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8822,10 +8817,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46102</v>
+        <v>45394</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8838,7 +8833,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8881,7 +8876,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8895,10 +8890,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44587</v>
+        <v>45225</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8911,7 +8906,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.6</v>
+        <v>3.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8971,7 +8966,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9027,7 +9022,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9041,10 +9036,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44946</v>
+        <v>45310</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9052,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9100,7 +9095,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9110,14 +9105,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46092</v>
+        <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9125,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9173,7 +9168,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9187,10 +9182,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45050</v>
+        <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9198,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9246,7 +9241,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9256,14 +9251,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45328</v>
+        <v>46287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9276,7 +9271,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9319,7 +9314,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9333,10 +9328,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44586</v>
+        <v>44637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9344,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9392,7 +9387,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9406,10 +9401,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45545</v>
+        <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9417,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9465,7 +9460,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9479,10 +9474,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44637</v>
+        <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9490,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9538,7 +9533,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9548,14 +9543,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45461</v>
+        <v>45356</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9563,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9611,7 +9606,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9625,10 +9620,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46258</v>
+        <v>45139</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9641,7 +9636,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9684,7 +9679,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9698,10 +9693,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46258</v>
+        <v>45139</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9709,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9757,7 +9752,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9771,10 +9766,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46258</v>
+        <v>45078</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9786,8 +9781,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45071</v>
+        <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45035</v>
+        <v>44649</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45303</v>
+        <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10049,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45259</v>
+        <v>45064</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44606</v>
+        <v>45194</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45769</v>
+        <v>45194</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10224,13 +10224,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10273,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10283,14 +10278,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45728</v>
+        <v>45397</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10303,7 +10298,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10346,7 +10341,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10360,10 +10355,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45394</v>
+        <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10376,7 +10371,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10419,7 +10414,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10433,10 +10428,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45194</v>
+        <v>45397</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10449,7 +10444,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10492,7 +10487,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10506,10 +10501,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45364</v>
+        <v>45035</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10522,7 +10517,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10565,7 +10560,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10579,10 +10574,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45383</v>
+        <v>45545</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10595,7 +10590,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10638,7 +10633,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39163-2026</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10652,10 +10647,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46287</v>
+        <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10667,8 +10662,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10711,7 +10711,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45193</v>
+        <v>45364</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10784,7 +10784,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45261</v>
+        <v>45383</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45832</v>
+        <v>45193</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>8.199999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10930,7 +10930,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45819</v>
+        <v>45261</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11020,7 +11020,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>46002</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45593</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>46013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44618</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46287</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>46287</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46090</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45456</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>46142</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44560</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>45756</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>45139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45226</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45259</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45932</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45769</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>46102</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46002</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45063</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45832</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45086</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45819</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>46171</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46178</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46178</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45382</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45328</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>46258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>46258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45394</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45225</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45310</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45356</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45139</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45139</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45078</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44649</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45064</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45194</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45194</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45397</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45397</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45035</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45545</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45364</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45383</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45193</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45261</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45182</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>46002</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>45601</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>45593</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>46013</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>44618</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>46191</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>45173</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>46287</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>46287</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>46090</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>45965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45456</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44973</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>46142</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44560</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>45756</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>45139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44465</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>45205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>45226</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>44946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>45260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>45394</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>46028</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44587</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>46055</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>45259</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44606</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>45932</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>46090</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>45769</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>46102</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>45328</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>46002</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>45063</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45832</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>45086</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>45819</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>46171</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46178</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45084</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>46178</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45382</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>45328</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         <v>45225</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8528,7 +8528,7 @@
         <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>46258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45728</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>46258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45394</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>45225</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>45310</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45000</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45356</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45139</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45139</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45078</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44649</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45107</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45064</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45194</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45194</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45397</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45397</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45035</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45545</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45756</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45364</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45383</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45193</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45261</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44872</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 55825-2023</t>
+          <t>A 42922-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45239</v>
+        <v>45182</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,169 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>47</v>
+      </c>
+      <c r="U5" t="n">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Ostticka
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Talltita
+Tjockfotad fingersvamp
+Björksplintborre
+Granbarkgnagare
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 55825-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45239</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>46</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>43</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1124,164 +1248,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="Z5">
+      <c r="Z6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 42922-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45182</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>47</v>
-      </c>
-      <c r="U6" t="n">
-        <v>47</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Ostticka
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Talltita
-Tjockfotad fingersvamp
-Björksplintborre
-Granbarkgnagare
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 61763-2025</t>
+          <t>A 50435-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46002</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,11 +1564,16 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1577,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1589,21 +1594,138 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Talltita
+Aprikosfingersvamp
+Mindre märgborre
+Mönjevaxing
+Nästrot
+Tibast
+Blåsippa
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 61763-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Dunmossa
@@ -1616,158 +1738,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 50435-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45601</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Talltita
-Aprikosfingersvamp
-Mindre märgborre
-Mönjevaxing
-Nästrot
-Tibast
-Blåsippa
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 63543-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>46013</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2409,597 +2409,597 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 27935-2026</t>
+          <t>A 41021-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46191</v>
+        <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3359,17 +3359,17 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3392,474 +3392,474 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 41021-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 39170-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="D28" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 39168-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 39168-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 39170-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45756</v>
+        <v>45450</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3888,13 +3888,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3934,42 +3929,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3983,10 +3978,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>45965</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3999,7 +3994,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>22.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4039,42 +4034,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4088,10 +4083,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46090</v>
+        <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4104,17 +4099,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -4128,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4140,50 +4135,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4197,10 +4188,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46090</v>
+        <v>44973</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4213,17 +4204,17 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
@@ -4237,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4249,50 +4240,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4306,10 +4293,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4322,7 +4309,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4362,42 +4349,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4411,10 +4398,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45965</v>
+        <v>46090</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4427,16 +4414,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>22.9</v>
+        <v>5.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4451,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4467,42 +4454,46 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4516,10 +4507,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45456</v>
+        <v>46090</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4532,16 +4523,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4556,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4572,42 +4563,46 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44973</v>
+        <v>45756</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4636,17 +4631,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4673,39 +4673,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
         <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4827,14 +4827,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46142</v>
+        <v>45139</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4880,49 +4880,49 @@
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44560</v>
+        <v>45456</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,23 +4951,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -4981,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4997,42 +4992,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5042,14 +5037,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45756</v>
+        <v>46142</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5061,23 +5056,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -5091,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5103,46 +5093,46 @@
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5156,10 +5146,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45139</v>
+        <v>44560</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5171,17 +5161,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5196,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5212,42 +5207,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45450</v>
+        <v>45756</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5276,8 +5271,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5310,42 +5310,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52377-2021</t>
+          <t>A 14725-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5737,14 +5737,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44465</v>
+        <v>44655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5800,7 +5800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14725-2022</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44655</v>
+        <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44603</v>
+        <v>45226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45205</v>
+        <v>45086</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45226</v>
+        <v>45193</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6106,10 +6106,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44946</v>
+        <v>45261</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6175,14 +6175,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45260</v>
+        <v>46002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45394</v>
+        <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46028</v>
+        <v>44917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44587</v>
+        <v>45932</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46055</v>
+        <v>45932</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45259</v>
+        <v>45819</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44606</v>
+        <v>45000</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45932</v>
+        <v>46028</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45932</v>
+        <v>45394</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46090</v>
+        <v>45756</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6851,8 +6851,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6895,7 +6900,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45769</v>
+        <v>45194</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6924,13 +6929,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45000</v>
+        <v>45107</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7056,14 +7056,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46102</v>
+        <v>45382</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45328</v>
+        <v>44649</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46002</v>
+        <v>46055</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45050</v>
+        <v>45084</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45063</v>
+        <v>46090</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45071</v>
+        <v>44597</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45461</v>
+        <v>46102</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44597</v>
+        <v>45260</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45832</v>
+        <v>45397</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7713,14 +7713,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45086</v>
+        <v>45356</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45819</v>
+        <v>45397</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46171</v>
+        <v>45225</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7878,13 +7878,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7927,7 +7922,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7941,10 +7936,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46178</v>
+        <v>45205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7957,7 +7952,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8000,7 +7995,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8014,10 +8009,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45084</v>
+        <v>45225</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8030,7 +8025,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8073,7 +8068,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8087,10 +8082,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46178</v>
+        <v>45310</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8156,14 +8151,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45382</v>
+        <v>45063</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8176,7 +8171,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8219,7 +8214,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8229,14 +8224,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45586</v>
+        <v>45328</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8249,7 +8244,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8292,7 +8287,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8306,10 +8301,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46092</v>
+        <v>45139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8322,7 +8317,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8365,7 +8360,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8375,14 +8370,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45328</v>
+        <v>45139</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8390,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45225</v>
+        <v>45000</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8463,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8511,7 +8506,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8525,10 +8520,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46258</v>
+        <v>44609</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8536,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8584,7 +8579,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8598,10 +8593,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46258</v>
+        <v>45586</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8614,7 +8609,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8657,7 +8652,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8671,10 +8666,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45728</v>
+        <v>45064</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8687,7 +8682,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8730,7 +8725,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46258</v>
+        <v>44706</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8760,7 +8755,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8803,7 +8798,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8817,10 +8812,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45394</v>
+        <v>45078</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8832,8 +8827,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45225</v>
+        <v>46171</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8905,8 +8905,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8963,10 +8968,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45450</v>
+        <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8979,7 +8984,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9022,7 +9027,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9036,10 +9041,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45310</v>
+        <v>45450</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9052,7 +9057,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9095,7 +9100,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9105,14 +9110,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44917</v>
+        <v>44946</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9125,7 +9130,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9168,7 +9173,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9182,10 +9187,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44586</v>
+        <v>46178</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9198,7 +9203,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9241,7 +9246,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 39163-2026</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9255,10 +9260,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46287</v>
+        <v>46178</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9271,7 +9276,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9314,7 +9319,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9328,10 +9333,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44637</v>
+        <v>45050</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9344,7 +9349,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9387,7 +9392,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9401,10 +9406,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44706</v>
+        <v>46092</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9417,7 +9422,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9460,7 +9465,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9470,14 +9475,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45000</v>
+        <v>45328</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9490,7 +9495,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9533,7 +9538,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9543,14 +9548,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45356</v>
+        <v>44586</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9563,7 +9568,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9606,7 +9611,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9620,10 +9625,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45139</v>
+        <v>45545</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9636,7 +9641,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9679,7 +9684,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9693,10 +9698,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45139</v>
+        <v>44637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9709,7 +9714,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9752,7 +9757,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9766,10 +9771,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45078</v>
+        <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9781,13 +9786,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44609</v>
+        <v>46258</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44649</v>
+        <v>46258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45107</v>
+        <v>46258</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10049,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45064</v>
+        <v>45071</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10136,10 +10136,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45194</v>
+        <v>45035</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45194</v>
+        <v>45303</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10278,14 +10278,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45397</v>
+        <v>45259</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10341,7 +10341,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45303</v>
+        <v>44606</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10414,7 +10414,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10428,10 +10428,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45397</v>
+        <v>45769</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10443,8 +10443,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10487,7 +10492,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10501,10 +10506,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45035</v>
+        <v>45728</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10522,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10560,7 +10565,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10574,10 +10579,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45545</v>
+        <v>45394</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10595,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10633,7 +10638,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10647,10 +10652,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45756</v>
+        <v>45194</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10662,13 +10667,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10728,7 +10728,7 @@
         <v>45364</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45383</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45193</v>
+        <v>46287</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10930,24 +10930,24 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>S 6321-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45261</v>
+        <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11000,10 +11000,10 @@
       </c>
       <c r="V120" s="2" t="inlineStr"/>
     </row>
-    <row r="121" ht="15" customHeight="1">
+    <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 6321-2022</t>
+          <t>S 2547-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11017,10 +11017,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44872</v>
+        <v>45911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11072,79 +11072,6 @@
         <v>0</v>
       </c>
       <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>S 2547-2025</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>45911</v>
-      </c>
-      <c r="E122" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 55825-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45182</v>
+        <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1066,45 +1066,173 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6</v>
-      </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>16</v>
       </c>
       <c r="T5" t="n">
+        <v>46</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knärot
+Talltita
+Ullticka
+Vedskivlav
+Björksplintborre
+Blodticka
+Flagellkvastmossa
+Jättesvampmal
+Mindre märgborre
+Vedticka
+Mattlummer
+Spillkråka
+Tjäder
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="Z5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16</v>
+      </c>
+      <c r="T6" t="n">
         <v>47</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>47</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1124,164 +1252,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 55825-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45239</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>16</v>
-      </c>
-      <c r="T6" t="n">
-        <v>46</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Knärot
-Talltita
-Ullticka
-Vedskivlav
-Björksplintborre
-Blodticka
-Flagellkvastmossa
-Jättesvampmal
-Mindre märgborre
-Vedticka
-Mattlummer
-Spillkråka
-Tjäder
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 55825-2023 artfynd.xlsx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 55825-2023 karta.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 55825-2023 georefererad karta.tif", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="Z6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 55825-2023 karta knärot.png", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 55825-2023 FSC-klagomål.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 55825-2023 FSC-klagomål mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 55825-2023 tillsynsbegäran.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 55825-2023 tillsynsbegäran mail.docx", "A 55825-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 55825-2023 prioriterade fågelarter.docx", "A 55825-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45217</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 50435-2024</t>
+          <t>A 61763-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45601</v>
+        <v>46002</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,16 +1564,11 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.3</v>
+        <v>6.9</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1582,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1594,21 +1589,143 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" t="n">
+        <v>9</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gränsticka
+Dunmossa
+Talltita
+Björksplintborre
+Blomkålssvamp
+Mörk husmossa
+Stubbspretmossa
+Vågbandad barkbock
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 50435-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
         <v>16</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>15</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Talltita
@@ -1621,153 +1738,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 61763-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46002</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gränsticka
-Dunmossa
-Talltita
-Björksplintborre
-Blomkålssvamp
-Mörk husmossa
-Stubbspretmossa
-Vågbandad barkbock
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>44613</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44923</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63543-2025</t>
+          <t>A 14508-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46013</v>
+        <v>45394</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2409,597 +2409,597 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hussvala
+Berggräsfjäril
+Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 48717-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45593</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 9807-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Järnsparv
+Grönsiska
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
 Björksplintborre</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 48717-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>45593</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="D20" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 9745-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44618</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="U21" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Vedticka
 Spillkråka</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 9807-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Järnsparv
-Grönsiska
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 14508-2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45394</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hussvala
-Berggräsfjäril
-Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46013</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>45173</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 34460-2023</t>
+          <t>A 27935-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45139</v>
+        <v>46191</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3465,16 +3465,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3498,156 +3498,156 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Motaggsvamp
 Orange taggsvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 39170-2026</t>
+          <t>A 39168-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3664,7 +3664,7 @@
         <v>46287</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,16 +3677,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3710,156 +3710,156 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 39170-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
         <v>5</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Tallticka</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 39168-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Ullticka
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 17348-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45450</v>
+        <v>45756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3888,8 +3888,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3929,42 +3934,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3978,10 +3983,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45965</v>
+        <v>45448</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3994,7 +3999,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>22.9</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4034,35 +4039,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
@@ -4086,7 +4091,7 @@
         <v>45965</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4174,7 +4179,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4188,10 +4193,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44973</v>
+        <v>45965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.5</v>
+        <v>22.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4240,46 +4245,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 24068-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4293,10 +4298,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45448</v>
+        <v>45456</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4309,7 +4314,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4345,46 +4350,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46090</v>
+        <v>44973</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4414,17 +4419,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.9</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4438,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4450,43 +4455,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
@@ -4510,7 +4511,7 @@
         <v>46090</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4602,7 +4603,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17348-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4616,10 +4617,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45756</v>
+        <v>46090</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4631,19 +4632,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4677,35 +4673,39 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17348-2025 artfynd.xlsx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17348-2025 karta.png", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17348-2025 georefererad karta.tif", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17348-2025 FSC-klagomål.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17348-2025 FSC-klagomål mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17348-2025 tillsynsbegäran.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17348-2025 tillsynsbegäran mail.docx", "A 17348-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
         <v>46142</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45139</v>
+        <v>44560</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4846,17 +4846,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4871,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4887,42 +4892,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 24068-2024</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4936,10 +4941,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45456</v>
+        <v>45756</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4951,17 +4956,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4976,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4985,42 +4995,42 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 24068-2024 artfynd.xlsx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 24068-2024 karta.png", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 24068-2024 georefererad karta.tif", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 24068-2024 FSC-klagomål.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 24068-2024 FSC-klagomål mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 24068-2024 tillsynsbegäran.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 24068-2024 tillsynsbegäran mail.docx", "A 24068-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
@@ -5044,7 +5054,7 @@
         <v>46142</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5132,7 +5142,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5146,10 +5156,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44560</v>
+        <v>45139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5161,23 +5171,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5191,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5207,42 +5212,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45756</v>
+        <v>45450</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5271,13 +5276,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5310,42 +5310,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>44655</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45226</v>
+        <v>45205</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45086</v>
+        <v>45226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 46381-2023</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45193</v>
+        <v>44946</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 61027-2023</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45261</v>
+        <v>45260</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7.1</v>
+        <v>2.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46002</v>
+        <v>45394</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45832</v>
+        <v>46028</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6321,14 +6321,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44917</v>
+        <v>44587</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45932</v>
+        <v>45259</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45932</v>
+        <v>45832</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45819</v>
+        <v>44606</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>45932</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46028</v>
+        <v>45932</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6763,10 +6763,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45394</v>
+        <v>45819</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45756</v>
+        <v>45769</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45194</v>
+        <v>45000</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45107</v>
+        <v>46055</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7056,14 +7056,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45382</v>
+        <v>46002</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7119,7 +7119,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7133,10 +7133,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44649</v>
+        <v>46090</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7206,10 +7206,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46055</v>
+        <v>45050</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45084</v>
+        <v>46102</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7338,7 +7338,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7352,10 +7352,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46090</v>
+        <v>45063</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44597</v>
+        <v>45071</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7498,10 +7498,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46102</v>
+        <v>45461</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7557,7 +7557,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45260</v>
+        <v>44597</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7640,14 +7640,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45397</v>
+        <v>45328</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7713,14 +7713,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45356</v>
+        <v>45086</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7776,7 +7776,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45397</v>
+        <v>45084</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7859,14 +7859,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45225</v>
+        <v>45382</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7922,7 +7922,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45205</v>
+        <v>45586</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7995,7 +7995,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45225</v>
+        <v>45328</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8068,7 +8068,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45310</v>
+        <v>45225</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8155,10 +8155,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45063</v>
+        <v>45728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8224,14 +8224,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45328</v>
+        <v>45394</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8287,7 +8287,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8301,10 +8301,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45139</v>
+        <v>46171</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8316,8 +8316,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8360,7 +8365,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8374,10 +8379,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45139</v>
+        <v>45225</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8390,7 +8395,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8433,7 +8438,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45000</v>
+        <v>46178</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8463,7 +8468,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8506,7 +8511,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8520,10 +8525,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44609</v>
+        <v>46178</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8536,7 +8541,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8579,7 +8584,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8593,10 +8598,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45586</v>
+        <v>45450</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8609,7 +8614,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8652,7 +8657,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8666,10 +8671,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45064</v>
+        <v>45310</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8682,7 +8687,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8725,7 +8730,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 12819-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44706</v>
+        <v>46092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8755,7 +8760,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8798,7 +8803,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8808,14 +8813,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45078</v>
+        <v>44917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8827,13 +8832,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46171</v>
+        <v>44586</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8905,13 +8905,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8954,7 +8949,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8968,10 +8963,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44587</v>
+        <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8984,7 +8979,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9027,7 +9022,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9041,10 +9036,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45450</v>
+        <v>44706</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9052,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9100,7 +9095,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9114,10 +9109,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44946</v>
+        <v>45000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9125,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9173,7 +9168,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9183,14 +9178,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46178</v>
+        <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9198,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9246,7 +9241,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 34736-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9260,10 +9255,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46178</v>
+        <v>46258</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9276,7 +9271,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9319,7 +9314,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 34750-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9333,10 +9328,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45050</v>
+        <v>46258</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9344,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9392,7 +9387,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 34720-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9406,10 +9401,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46092</v>
+        <v>46258</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9417,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9465,7 +9460,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9475,14 +9470,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45328</v>
+        <v>45139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9490,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9538,7 +9533,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9552,10 +9547,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44586</v>
+        <v>45139</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9563,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9611,7 +9606,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9625,10 +9620,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45545</v>
+        <v>45078</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9640,8 +9635,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9684,7 +9684,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9698,10 +9698,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44637</v>
+        <v>44609</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9757,7 +9757,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9771,10 +9771,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45461</v>
+        <v>44649</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46258</v>
+        <v>45107</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46258</v>
+        <v>45064</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46258</v>
+        <v>45194</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45071</v>
+        <v>45194</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10132,14 +10132,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45035</v>
+        <v>45397</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10212,7 +10212,7 @@
         <v>45303</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45259</v>
+        <v>45397</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>9.4</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10341,7 +10341,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44606</v>
+        <v>45035</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10414,7 +10414,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10428,10 +10428,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45769</v>
+        <v>45545</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10443,13 +10443,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10492,7 +10487,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10506,10 +10501,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45728</v>
+        <v>45756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10521,8 +10516,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10565,7 +10565,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 39163-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10579,10 +10579,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45394</v>
+        <v>46287</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10638,7 +10638,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45194</v>
+        <v>45364</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10711,7 +10711,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10073-2024</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45364</v>
+        <v>45383</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10784,7 +10784,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12621-2024</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45383</v>
+        <v>45193</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10857,7 +10857,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 39163-2026</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10871,10 +10871,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46287</v>
+        <v>45261</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10947,7 +10947,7 @@
         <v>44872</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>

--- a/Översikt VALLENTUNA.xlsx
+++ b/Översikt VALLENTUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE121"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45168</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         <v>45208</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45401</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45239</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 42922-2023</t>
+          <t>A 50718-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45182</v>
+        <v>45217</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1218,21 +1218,145 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>16</v>
       </c>
       <c r="T6" t="n">
+        <v>43</v>
+      </c>
+      <c r="U6" t="n">
+        <v>43</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Rosenticka
+Tallticka
+Ullticka
+Vedtrappmossa
+Brandticka
+Bronshjon
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Gulnål
+Rödgul trumpetsvamp
+Trådticka
+Vedticka
+Blåsippa
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 42922-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45182</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
         <v>47</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>47</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Ostticka
 Fjällig taggsvamp s.str.
@@ -1252,160 +1376,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 42922-2023 artfynd.xlsx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 42922-2023 karta.png", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 42922-2023 georefererad karta.tif", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 42922-2023 FSC-klagomål.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 42922-2023 FSC-klagomål mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 42922-2023 tillsynsbegäran.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 42922-2023 tillsynsbegäran mail.docx", "A 42922-2023")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 42922-2023 prioriterade fågelarter.docx", "A 42922-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 50718-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45217</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>43</v>
-      </c>
-      <c r="U7" t="n">
-        <v>43</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Rosenticka
-Tallticka
-Ullticka
-Vedtrappmossa
-Brandticka
-Bronshjon
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Gulnål
-Rödgul trumpetsvamp
-Trådticka
-Vedticka
-Blåsippa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50718-2023 artfynd.xlsx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50718-2023 karta.png", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50718-2023 georefererad karta.tif", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50718-2023 FSC-klagomål.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50718-2023 FSC-klagomål mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50718-2023 tillsynsbegäran.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50718-2023 tillsynsbegäran mail.docx", "A 50718-2023")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50718-2023 prioriterade fågelarter.docx", "A 50718-2023")</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>45756</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 61763-2025</t>
+          <t>A 50435-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46002</v>
+        <v>45601</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1564,11 +1564,16 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
@@ -1577,7 +1582,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1589,21 +1594,138 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
       </c>
       <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="n">
+        <v>15</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Talltita
+Aprikosfingersvamp
+Mindre märgborre
+Mönjevaxing
+Nästrot
+Tibast
+Blåsippa
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 61763-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gränsticka
 Dunmossa
@@ -1616,158 +1738,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 61763-2025 artfynd.xlsx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 61763-2025 karta.png", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 61763-2025 georefererad karta.tif", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 61763-2025 FSC-klagomål.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 61763-2025 FSC-klagomål mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 61763-2025 tillsynsbegäran.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 61763-2025 tillsynsbegäran mail.docx", "A 61763-2025")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 61763-2025 prioriterade fågelarter.docx", "A 61763-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 50435-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45601</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>16</v>
-      </c>
-      <c r="U10" t="n">
-        <v>15</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Talltita
-Aprikosfingersvamp
-Mindre märgborre
-Mönjevaxing
-Nästrot
-Tibast
-Blåsippa
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 50435-2024 artfynd.xlsx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 50435-2024 karta.png", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 50435-2024 georefererad karta.tif", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 50435-2024 FSC-klagomål.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 50435-2024 FSC-klagomål mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 50435-2024 tillsynsbegäran.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 50435-2024 tillsynsbegäran mail.docx", "A 50435-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 50435-2024 prioriterade fågelarter.docx", "A 50435-2024")</f>
         <v/>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
         <v>44536</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>44732</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8500-2022</t>
+          <t>A 62402-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44613</v>
+        <v>44923</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2030,19 +2030,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>4</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2054,10 +2054,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>6</v>
@@ -2066,9 +2066,119 @@
         <v>6</v>
       </c>
       <c r="U13" t="n">
+        <v>6</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Denisespindling
+Kryddspindling
+Motaggsvamp
+Orange taggsvamp
+Anisspindling
+Brandticka</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 62402-2022 artfynd.xlsx", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 62402-2022 karta.png", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 62402-2022 georefererad karta.tif", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 62402-2022 FSC-klagomål.docx", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 62402-2022 FSC-klagomål mail.docx", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 62402-2022 tillsynsbegäran.docx", "A 62402-2022")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 62402-2022 tillsynsbegäran mail.docx", "A 62402-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 8500-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44613</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Björksplintborre
@@ -2078,150 +2188,40 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 8500-2022 artfynd.xlsx", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 8500-2022 karta.png", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 8500-2022 georefererad karta.tif", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/knärot/A 8500-2022 karta knärot.png", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 8500-2022 FSC-klagomål.docx", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 8500-2022 FSC-klagomål mail.docx", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 8500-2022 tillsynsbegäran.docx", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 8500-2022 tillsynsbegäran mail.docx", "A 8500-2022")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 8500-2022 prioriterade fågelarter.docx", "A 8500-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62402-2022</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44923</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>6</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Denisespindling
-Kryddspindling
-Motaggsvamp
-Orange taggsvamp
-Anisspindling
-Brandticka</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 62402-2022 artfynd.xlsx", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 62402-2022 karta.png", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 62402-2022 georefererad karta.tif", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 62402-2022 FSC-klagomål.docx", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 62402-2022 FSC-klagomål mail.docx", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 62402-2022 tillsynsbegäran.docx", "A 62402-2022")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 62402-2022 tillsynsbegäran mail.docx", "A 62402-2022")</f>
         <v/>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
         <v>45517</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14508-2024</t>
+          <t>A 9745-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45394</v>
+        <v>44618</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2397,609 +2397,609 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 14508-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45394</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Hussvala
 Berggräsfjäril
 Mindre hackspett</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 14508-2024 artfynd.xlsx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 14508-2024 karta.png", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 14508-2024 georefererad karta.tif", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 14508-2024 FSC-klagomål.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 14508-2024 FSC-klagomål mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 14508-2024 tillsynsbegäran.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 14508-2024 tillsynsbegäran mail.docx", "A 14508-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 14508-2024 prioriterade fågelarter.docx", "A 14508-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 37456-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45156</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp
+Tjockfotad fingersvamp
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 63543-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Björksplintborre</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 48717-2024</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45593</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>6.2</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Tjäder
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 48717-2024 artfynd.xlsx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 48717-2024 karta.png", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 48717-2024 georefererad karta.tif", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 48717-2024 FSC-klagomål.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 48717-2024 FSC-klagomål mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 48717-2024 tillsynsbegäran.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 48717-2024 tillsynsbegäran mail.docx", "A 48717-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 48717-2024 prioriterade fågelarter.docx", "A 48717-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 9807-2026</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>46072</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>2.1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T21" t="n">
         <v>8</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Järnsparv
 Grönsiska
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9807-2026 artfynd.xlsx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9807-2026 karta.png", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9807-2026 georefererad karta.tif", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9807-2026 FSC-klagomål.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9807-2026 FSC-klagomål mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9807-2026 tillsynsbegäran.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9807-2026 tillsynsbegäran mail.docx", "A 9807-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9807-2026 prioriterade fågelarter.docx", "A 9807-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 63543-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Björksplintborre</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63543-2025 artfynd.xlsx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63543-2025 karta.png", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63543-2025 georefererad karta.tif", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63543-2025 FSC-klagomål.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63543-2025 FSC-klagomål mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63543-2025 tillsynsbegäran.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63543-2025 tillsynsbegäran mail.docx", "A 63543-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 37456-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45156</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp
-Tjockfotad fingersvamp
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 37456-2023 artfynd.xlsx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 37456-2023 karta.png", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 37456-2023 georefererad karta.tif", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 37456-2023 FSC-klagomål.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 37456-2023 FSC-klagomål mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 37456-2023 tillsynsbegäran.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 37456-2023 tillsynsbegäran mail.docx", "A 37456-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 9745-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44618</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 9745-2022 artfynd.xlsx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 9745-2022 karta.png", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 9745-2022 georefererad karta.tif", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 9745-2022 FSC-klagomål.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 9745-2022 FSC-klagomål mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 9745-2022 tillsynsbegäran.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 9745-2022 tillsynsbegäran mail.docx", "A 9745-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 9745-2022 prioriterade fågelarter.docx", "A 9745-2022")</f>
         <v/>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         <v>44560</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44616</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63539-2025</t>
+          <t>A 41021-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46013</v>
+        <v>45173</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3293,361 +3293,361 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
+          <t>Fjällig taggsvamp s.str.
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 34460-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp
+Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 63539-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>Tallticka
 Vårärt</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 63539-2025 artfynd.xlsx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 63539-2025 karta.png", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 63539-2025 georefererad karta.tif", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 63539-2025 FSC-klagomål.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 63539-2025 FSC-klagomål mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 63539-2025 tillsynsbegäran.docx", "A 63539-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 63539-2025 tillsynsbegäran mail.docx", "A 63539-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 41021-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27935-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 41021-2023 artfynd.xlsx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 41021-2023 karta.png", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 41021-2023 georefererad karta.tif", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 41021-2023 FSC-klagomål.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 41021-2023 FSC-klagomål mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 41021-2023 tillsynsbegäran.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 41021-2023 tillsynsbegäran mail.docx", "A 41021-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 27935-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46191</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>9</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 27935-2026 artfynd.xlsx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 27935-2026 karta.png", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 27935-2026 georefererad karta.tif", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 27935-2026 FSC-klagomål.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 27935-2026 FSC-klagomål mail.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 27935-2026 tillsynsbegäran.docx", "A 27935-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 27935-2026 tillsynsbegäran mail.docx", "A 27935-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 34460-2023</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Motaggsvamp
-Orange taggsvamp</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34460-2023 artfynd.xlsx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34460-2023 karta.png", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34460-2023 georefererad karta.tif", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34460-2023 FSC-klagomål.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34460-2023 FSC-klagomål mail.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34460-2023 tillsynsbegäran.docx", "A 34460-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34460-2023 tillsynsbegäran mail.docx", "A 34460-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 39168-2026</t>
+          <t>A 39170-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3664,7 +3664,7 @@
         <v>46287</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3677,16 +3677,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3710,149 +3710,149 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Tallticka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 39168-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VALLENTUNA</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Ullticka
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39168-2026 artfynd.xlsx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39168-2026 karta.png", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39168-2026 georefererad karta.tif", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39168-2026 FSC-klagomål.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39168-2026 FSC-klagomål mail.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39168-2026 tillsynsbegäran.docx", "A 39168-2026")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39168-2026 tillsynsbegäran mail.docx", "A 39168-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 39170-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>46287</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VALLENTUNA</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>2</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Tallticka</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 39170-2026 artfynd.xlsx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 39170-2026 karta.png", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 39170-2026 georefererad karta.tif", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 39170-2026 FSC-klagomål.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 39170-2026 FSC-klagomål mail.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 39170-2026 tillsynsbegäran.docx", "A 39170-2026")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 39170-2026 tillsynsbegäran mail.docx", "A 39170-2026")</f>
         <v/>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
         <v>45756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 22830-2024</t>
+          <t>A 17341-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45448</v>
+        <v>45756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3998,17 +3998,22 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4023,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4032,49 +4037,49 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54481-2025</t>
+          <t>A 7890-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4088,10 +4093,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45965</v>
+        <v>44973</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4104,7 +4109,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4140,46 +4145,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54460-2025</t>
+          <t>A 34458-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4193,10 +4198,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45965</v>
+        <v>45139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4209,7 +4214,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>22.9</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4245,39 +4250,39 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
         <v/>
       </c>
     </row>
@@ -4301,7 +4306,7 @@
         <v>45456</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4389,7 +4394,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7890-2023</t>
+          <t>A 22830-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44973</v>
+        <v>45448</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4419,7 +4424,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4455,46 +4460,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 7890-2023 artfynd.xlsx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 22830-2024 artfynd.xlsx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 7890-2023 karta.png", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 22830-2024 karta.png", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 7890-2023 georefererad karta.tif", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 22830-2024 georefererad karta.tif", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 7890-2023 FSC-klagomål.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 22830-2024 FSC-klagomål.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 7890-2023 FSC-klagomål mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 22830-2024 FSC-klagomål mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 7890-2023 tillsynsbegäran.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 22830-2024 tillsynsbegäran.docx", "A 22830-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 7890-2023 tillsynsbegäran mail.docx", "A 7890-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 22830-2024 tillsynsbegäran mail.docx", "A 22830-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12396-2026</t>
+          <t>A 21-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46090</v>
+        <v>44560</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4523,8 +4528,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4564,46 +4574,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12401-2026</t>
+          <t>A 23009-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4617,10 +4623,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46090</v>
+        <v>45450</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4633,13 +4639,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4673,46 +4679,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 20910-2026</t>
+          <t>A 54460-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4726,10 +4728,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46142</v>
+        <v>45965</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4742,17 +4744,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>22.9</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4766,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4782,42 +4784,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54460-2025 artfynd.xlsx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54460-2025 karta.png", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54460-2025 georefererad karta.tif", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54460-2025 FSC-klagomål.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54460-2025 FSC-klagomål mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54460-2025 tillsynsbegäran.docx", "A 54460-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54460-2025 tillsynsbegäran mail.docx", "A 54460-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21-2022</t>
+          <t>A 54481-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4831,10 +4833,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44560</v>
+        <v>45965</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4846,23 +4848,18 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4876,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4888,46 +4885,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 21-2022 artfynd.xlsx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 54481-2025 artfynd.xlsx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 21-2022 karta.png", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 54481-2025 karta.png", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 21-2022 georefererad karta.tif", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 54481-2025 georefererad karta.tif", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 21-2022 FSC-klagomål.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 54481-2025 FSC-klagomål.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 21-2022 FSC-klagomål mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 54481-2025 FSC-klagomål mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 21-2022 tillsynsbegäran.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 54481-2025 tillsynsbegäran.docx", "A 54481-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 21-2022 tillsynsbegäran mail.docx", "A 21-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 54481-2025 tillsynsbegäran mail.docx", "A 54481-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 17341-2025</t>
+          <t>A 12401-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4941,10 +4938,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45756</v>
+        <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4956,19 +4953,14 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4995,49 +4987,53 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 17341-2025 artfynd.xlsx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12401-2026 artfynd.xlsx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 17341-2025 karta.png", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12401-2026 karta.png", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 17341-2025 georefererad karta.tif", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12401-2026 georefererad karta.tif", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 17341-2025 FSC-klagomål.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12401-2026 FSC-klagomål.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 17341-2025 FSC-klagomål mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12401-2026 FSC-klagomål mail.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 17341-2025 tillsynsbegäran.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12401-2026 tillsynsbegäran.docx", "A 12401-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 17341-2025 tillsynsbegäran mail.docx", "A 17341-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12401-2026 tillsynsbegäran mail.docx", "A 12401-2026")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12401-2026 prioriterade fågelarter.docx", "A 12401-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20914-2026</t>
+          <t>A 12396-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5047,14 +5043,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46142</v>
+        <v>46090</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5067,16 +5063,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5091,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5100,49 +5096,53 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 12396-2026 artfynd.xlsx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 12396-2026 karta.png", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 12396-2026 georefererad karta.tif", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 12396-2026 FSC-klagomål.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 12396-2026 FSC-klagomål mail.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 12396-2026 tillsynsbegäran.docx", "A 12396-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 12396-2026 tillsynsbegäran mail.docx", "A 12396-2026")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/fåglar/A 12396-2026 prioriterade fågelarter.docx", "A 12396-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34458-2023</t>
+          <t>A 20910-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45139</v>
+        <v>46142</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5172,16 +5172,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5208,46 +5208,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 34458-2023 artfynd.xlsx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20910-2026 artfynd.xlsx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 34458-2023 karta.png", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20910-2026 karta.png", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 34458-2023 georefererad karta.tif", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20910-2026 georefererad karta.tif", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 34458-2023 FSC-klagomål.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20910-2026 FSC-klagomål.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 34458-2023 FSC-klagomål mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20910-2026 FSC-klagomål mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 34458-2023 tillsynsbegäran.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20910-2026 tillsynsbegäran.docx", "A 20910-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 34458-2023 tillsynsbegäran mail.docx", "A 34458-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20910-2026 tillsynsbegäran mail.docx", "A 20910-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23009-2024</t>
+          <t>A 20914-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45450</v>
+        <v>46142</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5277,17 +5277,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5310,42 +5310,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 23009-2024 artfynd.xlsx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/artfynd/A 20914-2026 artfynd.xlsx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 23009-2024 karta.png", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor/A 20914-2026 karta.png", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 23009-2024 georefererad karta.tif", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/kartor_geotiff/A 20914-2026 georefererad karta.tif", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 23009-2024 FSC-klagomål.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomål/A 20914-2026 FSC-klagomål.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 23009-2024 FSC-klagomål mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/klagomålsmail/A 20914-2026 FSC-klagomål mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 23009-2024 tillsynsbegäran.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsyn/A 20914-2026 tillsynsbegäran.docx", "A 20914-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 23009-2024 tillsynsbegäran mail.docx", "A 23009-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0115/tillsynsmail/A 20914-2026 tillsynsbegäran mail.docx", "A 20914-2026")</f>
         <v/>
       </c>
     </row>
@@ -5369,7 +5369,7 @@
         <v>44609</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 178-2022</t>
+          <t>A 242-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>44560</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 242-2022</t>
+          <t>A 178-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5593,7 +5593,7 @@
         <v>44560</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
         <v>44606</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14725-2022</t>
+          <t>A 7085-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5737,14 +5737,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44655</v>
+        <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5800,7 +5800,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7085-2022</t>
+          <t>A 14725-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5810,14 +5810,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44603</v>
+        <v>44655</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 49530-2023</t>
+          <t>A 8077-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45205</v>
+        <v>44609</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 52989-2023</t>
+          <t>A 29704-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45226</v>
+        <v>45107</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3078-2023</t>
+          <t>A 22683-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44946</v>
+        <v>45071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 60795-2023</t>
+          <t>A 47140-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6102,14 +6102,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45260</v>
+        <v>45586</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6165,7 +6165,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14480-2024</t>
+          <t>A 17411-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6179,10 +6179,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45394</v>
+        <v>45035</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6238,7 +6238,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 414-2026</t>
+          <t>A 12609-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6248,14 +6248,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46028</v>
+        <v>45382</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6311,7 +6311,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3937-2022</t>
+          <t>A 1385-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6325,10 +6325,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44587</v>
+        <v>45303</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6384,7 +6384,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60818-2023</t>
+          <t>A 13836-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45259</v>
+        <v>44649</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9.4</v>
+        <v>3.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6457,7 +6457,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30902-2025</t>
+          <t>A 60818-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6471,10 +6471,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45832</v>
+        <v>45259</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6530,7 +6530,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7264-2022</t>
+          <t>A 21765-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44606</v>
+        <v>45064</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48014-2025</t>
+          <t>A 21614-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6617,10 +6617,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45932</v>
+        <v>44706</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6676,7 +6676,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48038-2025</t>
+          <t>A 23986-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45932</v>
+        <v>45078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6705,8 +6705,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6749,7 +6754,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28431-2025</t>
+          <t>A 7264-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45819</v>
+        <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6779,7 +6784,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6822,7 +6827,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 19356-2025</t>
+          <t>A 52989-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6836,10 +6841,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45769</v>
+        <v>45226</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6851,13 +6856,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6900,7 +6900,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12562-2023</t>
+          <t>A 24707-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45000</v>
+        <v>45084</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6973,7 +6973,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6298-2026</t>
+          <t>A 26390-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6987,10 +6987,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46055</v>
+        <v>45086</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7046,7 +7046,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 61646-2025</t>
+          <t>A 19356-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46002</v>
+        <v>45769</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7075,8 +7075,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7119,7 +7124,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12400-2026</t>
+          <t>A 11950-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7133,10 +7138,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46090</v>
+        <v>45728</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7154,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7192,7 +7197,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 19503-2023</t>
+          <t>A 3937-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7206,10 +7211,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45050</v>
+        <v>44587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7227,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7265,7 +7270,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14799-2026</t>
+          <t>A 23013-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7279,10 +7284,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46102</v>
+        <v>45450</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7300,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7338,7 +7343,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21445-2023</t>
+          <t>A 14489-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7352,10 +7357,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45063</v>
+        <v>45394</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7373,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7411,7 +7416,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 22683-2023</t>
+          <t>A 3078-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7425,10 +7430,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45071</v>
+        <v>44946</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7446,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7484,7 +7489,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24943-2024</t>
+          <t>A 45499-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7498,10 +7503,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45461</v>
+        <v>45194</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7519,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7557,7 +7562,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5910-2022</t>
+          <t>A 10073-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7571,10 +7576,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44597</v>
+        <v>45364</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7592,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7630,7 +7635,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4804-2024</t>
+          <t>A 5910-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7640,14 +7645,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45328</v>
+        <v>44597</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7665,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7703,7 +7708,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26390-2023</t>
+          <t>A 12621-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7717,10 +7722,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45086</v>
+        <v>45383</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7738,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7776,7 +7781,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24707-2023</t>
+          <t>A 19503-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7790,10 +7795,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45084</v>
+        <v>45050</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7811,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7849,7 +7854,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12609-2024</t>
+          <t>A 46381-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7859,14 +7864,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45382</v>
+        <v>45193</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7879,7 +7884,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7922,7 +7927,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47140-2024</t>
+          <t>A 61027-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45586</v>
+        <v>45261</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7952,7 +7957,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>7.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7995,7 +8000,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 4803-2024</t>
+          <t>A 60795-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8009,10 +8014,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45328</v>
+        <v>45260</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8025,7 +8030,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8068,7 +8073,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52542-2023</t>
+          <t>A 4803-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8078,14 +8083,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45225</v>
+        <v>45328</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8141,7 +8146,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 11950-2025</t>
+          <t>A 14775-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8155,10 +8160,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45728</v>
+        <v>45397</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8171,7 +8176,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8214,7 +8219,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14489-2024</t>
+          <t>A 3698-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8228,10 +8233,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45394</v>
+        <v>44586</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8244,7 +8249,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8287,7 +8292,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24740-2026</t>
+          <t>A 38102-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8301,10 +8306,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46171</v>
+        <v>45545</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8316,13 +8321,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52562-2023</t>
+          <t>A 8787-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8375,14 +8375,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45225</v>
+        <v>45356</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 25740-2026</t>
+          <t>A 12234-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46178</v>
+        <v>44637</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8511,7 +8511,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 25752-2026</t>
+          <t>A 14782-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46178</v>
+        <v>45397</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8584,7 +8584,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 23013-2024</t>
+          <t>A 52562-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8598,10 +8598,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45450</v>
+        <v>45225</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8657,7 +8657,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 2318-2024</t>
+          <t>A 49530-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45310</v>
+        <v>45205</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12819-2026</t>
+          <t>A 24943-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46092</v>
+        <v>45461</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8803,7 +8803,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61742-2022</t>
+          <t>A 52542-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8813,14 +8813,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44917</v>
+        <v>45225</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 3698-2022</t>
+          <t>A 2318-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44586</v>
+        <v>45310</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8949,7 +8949,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 12234-2022</t>
+          <t>A 21445-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8963,10 +8963,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44637</v>
+        <v>45063</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21614-2022</t>
+          <t>A 61742-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9032,14 +9032,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44706</v>
+        <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9095,7 +9095,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12585-2023</t>
+          <t>A 30902-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45000</v>
+        <v>45832</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9168,7 +9168,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8787-2024</t>
+          <t>A 34441-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9178,14 +9178,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45356</v>
+        <v>45139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9241,7 +9241,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 34736-2026</t>
+          <t>A 34445-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9255,10 +9255,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46258</v>
+        <v>45139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9314,7 +9314,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 34750-2026</t>
+          <t>A 28431-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9328,10 +9328,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46258</v>
+        <v>45819</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9387,7 +9387,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 34720-2026</t>
+          <t>A 12585-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46258</v>
+        <v>45000</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9460,7 +9460,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34441-2023</t>
+          <t>A 48014-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9474,10 +9474,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45139</v>
+        <v>45932</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34445-2023</t>
+          <t>A 12562-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9547,10 +9547,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45139</v>
+        <v>45000</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9606,7 +9606,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23986-2023</t>
+          <t>A 14480-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45078</v>
+        <v>45394</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9635,13 +9635,8 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9684,7 +9679,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8077-2022</t>
+          <t>A 48038-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9698,10 +9693,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44609</v>
+        <v>45932</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9709,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9757,7 +9752,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 13836-2022</t>
+          <t>A 17340-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9771,10 +9766,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44649</v>
+        <v>45756</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9786,8 +9781,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9830,7 +9830,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29704-2023</t>
+          <t>A 45496-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45107</v>
+        <v>45194</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9903,7 +9903,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21765-2023</t>
+          <t>A 61646-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45064</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9976,7 +9976,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45496-2023</t>
+          <t>A 414-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9990,10 +9990,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45194</v>
+        <v>46028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10049,7 +10049,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 45499-2023</t>
+          <t>A 6298-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10063,10 +10063,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45194</v>
+        <v>46055</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10122,7 +10122,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14782-2024</t>
+          <t>A 12400-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10132,14 +10132,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45397</v>
+        <v>46090</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1385-2024</t>
+          <t>A 14799-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45303</v>
+        <v>46102</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10268,7 +10268,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14775-2024</t>
+          <t>A 4804-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10278,14 +10278,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45397</v>
+        <v>45328</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10341,7 +10341,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17411-2023</t>
+          <t>A 24740-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10355,10 +10355,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45035</v>
+        <v>46171</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10370,8 +10370,13 @@
           <t>VALLENTUNA</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>5.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10414,7 +10419,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 38102-2024</t>
+          <t>A 25740-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10428,10 +10433,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45545</v>
+        <v>46178</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10449,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10487,7 +10492,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17340-2025</t>
+          <t>A 25752-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10501,10 +10506,10 @@
         </is>
       </c>
       <c r="D114" s="1"